--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F70A37D-631B-4E07-8A7D-832707EDAC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD689484-E022-4919-B4C3-840431C614D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4455" yWindow="2190" windowWidth="16365" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="198">
   <si>
     <t>No.</t>
   </si>
@@ -392,9 +392,6 @@
   </si>
   <si>
     <t>可攻击全场的任意目标，弹道无视障碍/单位/墓碑阻挡与嘲讽（被贴身时仍受远程限制）。</t>
-  </si>
-  <si>
-    <t>害怕被贴身</t>
   </si>
   <si>
     <t>宿魂</t>
@@ -1843,26 +1840,26 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2193,22 +2190,22 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.2">
@@ -2329,10 +2326,10 @@
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="3">
@@ -2467,7 +2464,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>27</v>
@@ -2516,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
@@ -2653,7 +2650,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>36</v>
@@ -3421,7 +3418,7 @@
         <v>26</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>78</v>
@@ -3521,7 +3518,7 @@
         <v>85</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
@@ -3564,7 +3561,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>87</v>
@@ -3615,7 +3612,7 @@
         <v>88</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -3801,16 +3798,16 @@
         <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>97</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -3858,7 +3855,7 @@
         <v>99</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
@@ -3901,7 +3898,7 @@
         <v>20</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G37" s="9" t="s">
         <v>101</v>
@@ -4332,9 +4329,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="7"/>
-      <c r="I46" s="7" t="s">
-        <v>121</v>
-      </c>
+      <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="3">
@@ -4366,7 +4361,7 @@
         <v>79</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D47" s="9">
         <v>2</v>
@@ -4375,10 +4370,10 @@
         <v>19</v>
       </c>
       <c r="F47" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -4413,7 +4408,7 @@
         <v>79</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D48" s="7">
         <v>0</v>
@@ -4425,10 +4420,10 @@
         <v>16</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
@@ -4456,13 +4451,13 @@
     </row>
     <row r="49" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="C49" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -4472,7 +4467,7 @@
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
@@ -4493,7 +4488,7 @@
     </row>
     <row r="58" spans="1:17" ht="27" x14ac:dyDescent="0.2">
       <c r="A58" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
@@ -4502,164 +4497,164 @@
       <c r="F58" s="20"/>
     </row>
     <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
+      <c r="A59" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:17" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B60" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="B60" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
     </row>
     <row r="61" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A61" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
-      <c r="P61" s="18"/>
-      <c r="Q61" s="18"/>
+        <v>192</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
+      <c r="K61" s="23"/>
+      <c r="L61" s="23"/>
+      <c r="M61" s="23"/>
+      <c r="N61" s="23"/>
+      <c r="O61" s="23"/>
+      <c r="P61" s="23"/>
+      <c r="Q61" s="23"/>
     </row>
     <row r="62" spans="1:17" ht="18" x14ac:dyDescent="0.2">
       <c r="A62" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
-      <c r="K62" s="19"/>
-      <c r="L62" s="19"/>
-      <c r="M62" s="19"/>
-      <c r="N62" s="19"/>
-      <c r="O62" s="19"/>
-      <c r="P62" s="19"/>
-      <c r="Q62" s="19"/>
+        <v>166</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="22"/>
+      <c r="N62" s="22"/>
+      <c r="O62" s="22"/>
+      <c r="P62" s="22"/>
+      <c r="Q62" s="22"/>
     </row>
     <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
-      <c r="K63" s="19"/>
-      <c r="L63" s="19"/>
-      <c r="M63" s="19"/>
-      <c r="N63" s="19"/>
-      <c r="O63" s="19"/>
-      <c r="P63" s="19"/>
-      <c r="Q63" s="19"/>
+        <v>173</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="22"/>
+      <c r="M63" s="22"/>
+      <c r="N63" s="22"/>
+      <c r="O63" s="22"/>
+      <c r="P63" s="22"/>
+      <c r="Q63" s="22"/>
     </row>
     <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="B64" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="19"/>
-      <c r="M64" s="19"/>
-      <c r="N64" s="19"/>
-      <c r="O64" s="19"/>
-      <c r="P64" s="19"/>
-      <c r="Q64" s="19"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="22"/>
+      <c r="P64" s="22"/>
+      <c r="Q64" s="22"/>
     </row>
     <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B65" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="B65" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
-      <c r="K65" s="19"/>
-      <c r="L65" s="19"/>
-      <c r="M65" s="19"/>
-      <c r="N65" s="19"/>
-      <c r="O65" s="19"/>
-      <c r="P65" s="19"/>
-      <c r="Q65" s="19"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="22"/>
+      <c r="O65" s="22"/>
+      <c r="P65" s="22"/>
+      <c r="Q65" s="22"/>
     </row>
     <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="B66" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="19"/>
-      <c r="L66" s="19"/>
-      <c r="M66" s="19"/>
-      <c r="N66" s="19"/>
-      <c r="O66" s="19"/>
-      <c r="P66" s="19"/>
-      <c r="Q66" s="19"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="22"/>
+      <c r="J66" s="22"/>
+      <c r="K66" s="22"/>
+      <c r="L66" s="22"/>
+      <c r="M66" s="22"/>
+      <c r="N66" s="22"/>
+      <c r="O66" s="22"/>
+      <c r="P66" s="22"/>
+      <c r="Q66" s="22"/>
     </row>
     <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="14"/>
@@ -4670,8 +4665,8 @@
       <c r="F67" s="14"/>
     </row>
     <row r="68" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A68" s="23" t="s">
-        <v>196</v>
+      <c r="A68" s="19" t="s">
+        <v>195</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -4681,220 +4676,220 @@
     </row>
     <row r="69" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A69" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B69" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="18"/>
-      <c r="L69" s="18"/>
-      <c r="M69" s="18"/>
-      <c r="N69" s="18"/>
-      <c r="O69" s="18"/>
-      <c r="P69" s="18"/>
-      <c r="Q69" s="18"/>
+        <v>196</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
+      <c r="H69" s="23"/>
+      <c r="I69" s="23"/>
+      <c r="J69" s="23"/>
+      <c r="K69" s="23"/>
+      <c r="L69" s="23"/>
+      <c r="M69" s="23"/>
+      <c r="N69" s="23"/>
+      <c r="O69" s="23"/>
+      <c r="P69" s="23"/>
+      <c r="Q69" s="23"/>
     </row>
     <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
-      <c r="K70" s="19"/>
-      <c r="L70" s="19"/>
-      <c r="M70" s="19"/>
-      <c r="N70" s="19"/>
-      <c r="O70" s="19"/>
-      <c r="P70" s="19"/>
-      <c r="Q70" s="19"/>
+        <v>174</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
+      <c r="P70" s="22"/>
+      <c r="Q70" s="22"/>
     </row>
     <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="C71" s="19"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19"/>
-      <c r="K71" s="19"/>
-      <c r="L71" s="19"/>
-      <c r="M71" s="19"/>
-      <c r="N71" s="19"/>
-      <c r="O71" s="19"/>
-      <c r="P71" s="19"/>
-      <c r="Q71" s="19"/>
+        <v>175</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
     </row>
     <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19"/>
-      <c r="K72" s="19"/>
-      <c r="L72" s="19"/>
-      <c r="M72" s="19"/>
-      <c r="N72" s="19"/>
-      <c r="O72" s="19"/>
-      <c r="P72" s="19"/>
-      <c r="Q72" s="19"/>
+        <v>176</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="B73" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
-      <c r="K73" s="19"/>
-      <c r="L73" s="19"/>
-      <c r="M73" s="19"/>
-      <c r="N73" s="19"/>
-      <c r="O73" s="19"/>
-      <c r="P73" s="19"/>
-      <c r="Q73" s="19"/>
+        <v>177</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
+      <c r="P73" s="22"/>
+      <c r="Q73" s="22"/>
     </row>
     <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
-      <c r="K74" s="19"/>
-      <c r="L74" s="19"/>
-      <c r="M74" s="19"/>
-      <c r="N74" s="19"/>
-      <c r="O74" s="19"/>
-      <c r="P74" s="19"/>
-      <c r="Q74" s="19"/>
+        <v>178</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
     </row>
     <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="19"/>
-      <c r="K75" s="19"/>
-      <c r="L75" s="19"/>
-      <c r="M75" s="19"/>
-      <c r="N75" s="19"/>
-      <c r="O75" s="19"/>
-      <c r="P75" s="19"/>
-      <c r="Q75" s="19"/>
+        <v>179</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="22"/>
+      <c r="K75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
     </row>
     <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19"/>
-      <c r="K76" s="19"/>
-      <c r="L76" s="19"/>
-      <c r="M76" s="19"/>
-      <c r="N76" s="19"/>
-      <c r="O76" s="19"/>
-      <c r="P76" s="19"/>
-      <c r="Q76" s="19"/>
+        <v>180</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
     </row>
     <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B77" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="B77" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="19"/>
-      <c r="K77" s="19"/>
-      <c r="L77" s="19"/>
-      <c r="M77" s="19"/>
-      <c r="N77" s="19"/>
-      <c r="O77" s="19"/>
-      <c r="P77" s="19"/>
-      <c r="Q77" s="19"/>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
+      <c r="K77" s="22"/>
+      <c r="L77" s="22"/>
+      <c r="M77" s="22"/>
+      <c r="N77" s="22"/>
+      <c r="O77" s="22"/>
+      <c r="P77" s="22"/>
+      <c r="Q77" s="22"/>
     </row>
     <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
+      <c r="A78" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -4903,6 +4898,10 @@
     </sortState>
   </autoFilter>
   <mergeCells count="20">
+    <mergeCell ref="B73:Q73"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="B64:Q64"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="B60:F60"/>
@@ -4919,10 +4918,6 @@
     <mergeCell ref="B69:Q69"/>
     <mergeCell ref="B71:Q71"/>
     <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="B73:Q73"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="B64:Q64"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4939,10 +4934,10 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -4950,26 +4945,26 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E12">
         <v>18.75</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H12" s="25"/>
       <c r="J12" s="25"/>
@@ -4977,19 +4972,19 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" t="s">
         <v>133</v>
       </c>
-      <c r="D13" t="s">
-        <v>134</v>
-      </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G13" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" t="s">
         <v>141</v>
-      </c>
-      <c r="H13" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -5005,7 +5000,7 @@
         <v>18.75</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5024,7 +5019,7 @@
         <v>18.75</v>
       </c>
       <c r="G15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -5043,7 +5038,7 @@
         <v>18.75</v>
       </c>
       <c r="G16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -5062,7 +5057,7 @@
         <v>18.75</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -5081,7 +5076,7 @@
         <v>18.75</v>
       </c>
       <c r="G18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H18">
         <v>0</v>

--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD689484-E022-4919-B4C3-840431C614D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D301FED-8056-4F13-BE43-618BD4702FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4455" yWindow="2190" windowWidth="16365" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="199">
   <si>
     <t>No.</t>
   </si>
@@ -1591,6 +1591,10 @@
   </si>
   <si>
     <t>面板攻击力可以大于等于4的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复仇者</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1840,26 +1844,26 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4376,7 +4380,9 @@
         <v>123</v>
       </c>
       <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
+      <c r="I47" s="12" t="s">
+        <v>198</v>
+      </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
       <c r="L47" s="3">
@@ -4487,174 +4493,174 @@
       <c r="Q49" s="3"/>
     </row>
     <row r="58" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
     </row>
     <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="24" t="s">
+      <c r="A59" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
     </row>
     <row r="60" spans="1:17" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
     </row>
     <row r="61" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A61" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="B61" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23"/>
-      <c r="J61" s="23"/>
-      <c r="K61" s="23"/>
-      <c r="L61" s="23"/>
-      <c r="M61" s="23"/>
-      <c r="N61" s="23"/>
-      <c r="O61" s="23"/>
-      <c r="P61" s="23"/>
-      <c r="Q61" s="23"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="18" x14ac:dyDescent="0.2">
       <c r="A62" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="22"/>
-      <c r="O62" s="22"/>
-      <c r="P62" s="22"/>
-      <c r="Q62" s="22"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
     </row>
     <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="22"/>
-      <c r="N63" s="22"/>
-      <c r="O63" s="22"/>
-      <c r="P63" s="22"/>
-      <c r="Q63" s="22"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
+      <c r="P63" s="18"/>
+      <c r="Q63" s="18"/>
     </row>
     <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
-      <c r="J64" s="22"/>
-      <c r="K64" s="22"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="22"/>
-      <c r="N64" s="22"/>
-      <c r="O64" s="22"/>
-      <c r="P64" s="22"/>
-      <c r="Q64" s="22"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+      <c r="P64" s="18"/>
+      <c r="Q64" s="18"/>
     </row>
     <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-      <c r="L65" s="22"/>
-      <c r="M65" s="22"/>
-      <c r="N65" s="22"/>
-      <c r="O65" s="22"/>
-      <c r="P65" s="22"/>
-      <c r="Q65" s="22"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
+      <c r="L65" s="18"/>
+      <c r="M65" s="18"/>
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="18"/>
     </row>
     <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
-      <c r="I66" s="22"/>
-      <c r="J66" s="22"/>
-      <c r="K66" s="22"/>
-      <c r="L66" s="22"/>
-      <c r="M66" s="22"/>
-      <c r="N66" s="22"/>
-      <c r="O66" s="22"/>
-      <c r="P66" s="22"/>
-      <c r="Q66" s="22"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="18"/>
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+      <c r="P66" s="18"/>
+      <c r="Q66" s="18"/>
     </row>
     <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="14"/>
@@ -4665,231 +4671,231 @@
       <c r="F67" s="14"/>
     </row>
     <row r="68" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A68" s="19" t="s">
+      <c r="A68" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
     </row>
     <row r="69" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A69" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="23"/>
-      <c r="I69" s="23"/>
-      <c r="J69" s="23"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="23"/>
-      <c r="N69" s="23"/>
-      <c r="O69" s="23"/>
-      <c r="P69" s="23"/>
-      <c r="Q69" s="23"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="24"/>
+      <c r="N69" s="24"/>
+      <c r="O69" s="24"/>
+      <c r="P69" s="24"/>
+      <c r="Q69" s="24"/>
     </row>
     <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="B70" s="22" t="s">
+      <c r="B70" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
-      <c r="L70" s="22"/>
-      <c r="M70" s="22"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="22"/>
-      <c r="P70" s="22"/>
-      <c r="Q70" s="22"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="18"/>
+      <c r="Q70" s="18"/>
     </row>
     <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="B71" s="22" t="s">
+      <c r="B71" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="22"/>
-      <c r="P71" s="22"/>
-      <c r="Q71" s="22"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
+      <c r="M71" s="18"/>
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
+      <c r="P71" s="18"/>
+      <c r="Q71" s="18"/>
     </row>
     <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B72" s="22" t="s">
+      <c r="B72" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="22"/>
-      <c r="K72" s="22"/>
-      <c r="L72" s="22"/>
-      <c r="M72" s="22"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="22"/>
-      <c r="P72" s="22"/>
-      <c r="Q72" s="22"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="18"/>
+      <c r="Q72" s="18"/>
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="22"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="18"/>
+      <c r="Q73" s="18"/>
     </row>
     <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="22"/>
-      <c r="L74" s="22"/>
-      <c r="M74" s="22"/>
-      <c r="N74" s="22"/>
-      <c r="O74" s="22"/>
-      <c r="P74" s="22"/>
-      <c r="Q74" s="22"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
+      <c r="P74" s="18"/>
+      <c r="Q74" s="18"/>
     </row>
     <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="22"/>
-      <c r="L75" s="22"/>
-      <c r="M75" s="22"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="22"/>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
+      <c r="L75" s="18"/>
+      <c r="M75" s="18"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+      <c r="P75" s="18"/>
+      <c r="Q75" s="18"/>
     </row>
     <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="B76" s="22" t="s">
+      <c r="B76" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="22"/>
-      <c r="J76" s="22"/>
-      <c r="K76" s="22"/>
-      <c r="L76" s="22"/>
-      <c r="M76" s="22"/>
-      <c r="N76" s="22"/>
-      <c r="O76" s="22"/>
-      <c r="P76" s="22"/>
-      <c r="Q76" s="22"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="18"/>
+      <c r="H76" s="18"/>
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="18"/>
+      <c r="L76" s="18"/>
+      <c r="M76" s="18"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="18"/>
+      <c r="P76" s="18"/>
+      <c r="Q76" s="18"/>
     </row>
     <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B77" s="22" t="s">
+      <c r="B77" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="22"/>
-      <c r="J77" s="22"/>
-      <c r="K77" s="22"/>
-      <c r="L77" s="22"/>
-      <c r="M77" s="22"/>
-      <c r="N77" s="22"/>
-      <c r="O77" s="22"/>
-      <c r="P77" s="22"/>
-      <c r="Q77" s="22"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
+      <c r="P77" s="18"/>
+      <c r="Q77" s="18"/>
     </row>
     <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="18" t="s">
+      <c r="A78" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
-      <c r="F78" s="18"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -4898,6 +4904,10 @@
     </sortState>
   </autoFilter>
   <mergeCells count="20">
+    <mergeCell ref="B61:Q61"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:Q71"/>
+    <mergeCell ref="B72:Q72"/>
     <mergeCell ref="B73:Q73"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A59:F59"/>
@@ -4914,10 +4924,6 @@
     <mergeCell ref="B70:Q70"/>
     <mergeCell ref="B76:Q76"/>
     <mergeCell ref="B77:Q77"/>
-    <mergeCell ref="B61:Q61"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:Q71"/>
-    <mergeCell ref="B72:Q72"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -406,7 +406,7 @@
     <t>共鸣者</t>
   </si>
   <si>
-    <t>我方回合开始时，攻击力增加所有队友攻击力之和，直到我方回合结束。</t>
+    <t>我方回合开始时，攻击力变为所有队友攻击力之和，直到我方回合结束。</t>
   </si>
   <si>
     <t>—</t>

--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D301FED-8056-4F13-BE43-618BD4702FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B989E7C-DFE7-43F1-BAC4-D636769015C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4455" yWindow="2190" windowWidth="16365" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,9 +286,6 @@
     <t>古灵精怪</t>
   </si>
   <si>
-    <t>对方回合结束时，随机变为己方队伍中的一名其他角色（可以和上场角色重复，可以是已经退场角色），暂时获得其所有技能直到下次变化为止。</t>
-  </si>
-  <si>
     <t>太阳斩</t>
   </si>
   <si>
@@ -1595,6 +1592,10 @@
   </si>
   <si>
     <t>复仇者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对方回合结束时，随机变为己方队伍中的一名其他角色，暂时获得其所有技能和特性，直到下次变化为止。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1844,6 +1845,9 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1861,9 +1865,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2194,22 +2195,22 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.2">
@@ -2330,10 +2331,10 @@
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="3">
@@ -2468,7 +2469,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>27</v>
@@ -2517,7 +2518,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
@@ -2654,7 +2655,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>36</v>
@@ -3422,7 +3423,7 @@
         <v>26</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>78</v>
@@ -3501,7 +3502,7 @@
         <v>21.900000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="69" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -3518,11 +3519,11 @@
         <v>18</v>
       </c>
       <c r="F29" s="9"/>
-      <c r="G29" s="9" t="s">
-        <v>85</v>
+      <c r="G29" s="13" t="s">
+        <v>198</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
@@ -3556,7 +3557,7 @@
         <v>79</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D30" s="7">
         <v>3</v>
@@ -3565,10 +3566,10 @@
         <v>16</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -3613,10 +3614,10 @@
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -3650,7 +3651,7 @@
         <v>79</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D32" s="7">
         <v>3</v>
@@ -3659,10 +3660,10 @@
         <v>18</v>
       </c>
       <c r="F32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -3697,7 +3698,7 @@
         <v>79</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="9">
         <v>2</v>
@@ -3707,7 +3708,7 @@
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>33</v>
@@ -3756,10 +3757,10 @@
         <v>23</v>
       </c>
       <c r="G34" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -3793,7 +3794,7 @@
         <v>79</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="9">
         <v>3</v>
@@ -3802,16 +3803,16 @@
         <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -3844,7 +3845,7 @@
         <v>79</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="7">
         <v>3</v>
@@ -3856,10 +3857,10 @@
         <v>23</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
@@ -3893,7 +3894,7 @@
         <v>79</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D37" s="9">
         <v>2</v>
@@ -3902,10 +3903,10 @@
         <v>20</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -3937,10 +3938,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="D38" s="7">
         <v>2</v>
@@ -3950,7 +3951,7 @@
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>42</v>
@@ -3984,10 +3985,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D39" s="9">
         <v>0</v>
@@ -3996,10 +3997,10 @@
         <v>27</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -4031,10 +4032,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D40" s="7">
         <v>3</v>
@@ -4046,7 +4047,7 @@
         <v>51</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
@@ -4078,10 +4079,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D41" s="9">
         <v>5</v>
@@ -4091,7 +4092,7 @@
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -4123,10 +4124,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D42" s="7">
         <v>2</v>
@@ -4136,7 +4137,7 @@
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>66</v>
@@ -4170,10 +4171,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D43" s="9">
         <v>2</v>
@@ -4185,7 +4186,7 @@
         <v>16</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -4217,7 +4218,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>73</v>
@@ -4232,7 +4233,7 @@
         <v>23</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -4269,7 +4270,7 @@
         <v>79</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D45" s="9">
         <v>2</v>
@@ -4281,11 +4282,11 @@
         <v>38</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
@@ -4318,7 +4319,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D46" s="7">
         <v>3</v>
@@ -4330,7 +4331,7 @@
         <v>23</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
@@ -4365,7 +4366,7 @@
         <v>79</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D47" s="9">
         <v>2</v>
@@ -4374,14 +4375,14 @@
         <v>19</v>
       </c>
       <c r="F47" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
@@ -4414,7 +4415,7 @@
         <v>79</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D48" s="7">
         <v>0</v>
@@ -4426,10 +4427,10 @@
         <v>16</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
@@ -4457,13 +4458,13 @@
     </row>
     <row r="49" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="C49" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -4473,7 +4474,7 @@
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
@@ -4493,174 +4494,174 @@
       <c r="Q49" s="3"/>
     </row>
     <row r="58" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A58" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
+      <c r="A58" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
     </row>
     <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
+      <c r="A59" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
     </row>
     <row r="60" spans="1:17" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B60" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="B60" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A61" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+        <v>191</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="18"/>
+      <c r="Q61" s="18"/>
     </row>
     <row r="62" spans="1:17" ht="18" x14ac:dyDescent="0.2">
       <c r="A62" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="18"/>
-      <c r="I62" s="18"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="18"/>
-      <c r="L62" s="18"/>
-      <c r="M62" s="18"/>
-      <c r="N62" s="18"/>
-      <c r="O62" s="18"/>
-      <c r="P62" s="18"/>
-      <c r="Q62" s="18"/>
+        <v>165</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="19"/>
+      <c r="M62" s="19"/>
+      <c r="N62" s="19"/>
+      <c r="O62" s="19"/>
+      <c r="P62" s="19"/>
+      <c r="Q62" s="19"/>
     </row>
     <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="18"/>
-      <c r="P63" s="18"/>
-      <c r="Q63" s="18"/>
+        <v>172</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="19"/>
+      <c r="M63" s="19"/>
+      <c r="N63" s="19"/>
+      <c r="O63" s="19"/>
+      <c r="P63" s="19"/>
+      <c r="Q63" s="19"/>
     </row>
     <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B64" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B64" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
-      <c r="P64" s="18"/>
-      <c r="Q64" s="18"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
     </row>
     <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B65" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="B65" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
-      <c r="P65" s="18"/>
-      <c r="Q65" s="18"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="19"/>
+      <c r="O65" s="19"/>
+      <c r="P65" s="19"/>
+      <c r="Q65" s="19"/>
     </row>
     <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B66" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="B66" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="18"/>
-      <c r="P66" s="18"/>
-      <c r="Q66" s="18"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="19"/>
+      <c r="O66" s="19"/>
+      <c r="P66" s="19"/>
+      <c r="Q66" s="19"/>
     </row>
     <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="14"/>
@@ -4671,231 +4672,231 @@
       <c r="F67" s="14"/>
     </row>
     <row r="68" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A68" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
+      <c r="A68" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
     </row>
     <row r="69" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A69" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B69" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="24"/>
-      <c r="K69" s="24"/>
-      <c r="L69" s="24"/>
-      <c r="M69" s="24"/>
-      <c r="N69" s="24"/>
-      <c r="O69" s="24"/>
-      <c r="P69" s="24"/>
-      <c r="Q69" s="24"/>
+        <v>195</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
+      <c r="M69" s="18"/>
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
+      <c r="P69" s="18"/>
+      <c r="Q69" s="18"/>
     </row>
     <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="B70" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
-      <c r="H70" s="18"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-      <c r="N70" s="18"/>
-      <c r="O70" s="18"/>
-      <c r="P70" s="18"/>
-      <c r="Q70" s="18"/>
+        <v>173</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="19"/>
+      <c r="M70" s="19"/>
+      <c r="N70" s="19"/>
+      <c r="O70" s="19"/>
+      <c r="P70" s="19"/>
+      <c r="Q70" s="19"/>
     </row>
     <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="B71" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
-      <c r="N71" s="18"/>
-      <c r="O71" s="18"/>
-      <c r="P71" s="18"/>
-      <c r="Q71" s="18"/>
+        <v>174</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="19"/>
+      <c r="M71" s="19"/>
+      <c r="N71" s="19"/>
+      <c r="O71" s="19"/>
+      <c r="P71" s="19"/>
+      <c r="Q71" s="19"/>
     </row>
     <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="B72" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="18"/>
-      <c r="H72" s="18"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="18"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
-      <c r="N72" s="18"/>
-      <c r="O72" s="18"/>
-      <c r="P72" s="18"/>
-      <c r="Q72" s="18"/>
+        <v>175</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="19"/>
+      <c r="M72" s="19"/>
+      <c r="N72" s="19"/>
+      <c r="O72" s="19"/>
+      <c r="P72" s="19"/>
+      <c r="Q72" s="19"/>
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="B73" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="18"/>
-      <c r="H73" s="18"/>
-      <c r="I73" s="18"/>
-      <c r="J73" s="18"/>
-      <c r="K73" s="18"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
-      <c r="N73" s="18"/>
-      <c r="O73" s="18"/>
-      <c r="P73" s="18"/>
-      <c r="Q73" s="18"/>
+        <v>176</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
+      <c r="K73" s="19"/>
+      <c r="L73" s="19"/>
+      <c r="M73" s="19"/>
+      <c r="N73" s="19"/>
+      <c r="O73" s="19"/>
+      <c r="P73" s="19"/>
+      <c r="Q73" s="19"/>
     </row>
     <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="B74" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="18"/>
-      <c r="I74" s="18"/>
-      <c r="J74" s="18"/>
-      <c r="K74" s="18"/>
-      <c r="L74" s="18"/>
-      <c r="M74" s="18"/>
-      <c r="N74" s="18"/>
-      <c r="O74" s="18"/>
-      <c r="P74" s="18"/>
-      <c r="Q74" s="18"/>
+        <v>177</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="19"/>
+      <c r="M74" s="19"/>
+      <c r="N74" s="19"/>
+      <c r="O74" s="19"/>
+      <c r="P74" s="19"/>
+      <c r="Q74" s="19"/>
     </row>
     <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="B75" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
-      <c r="H75" s="18"/>
-      <c r="I75" s="18"/>
-      <c r="J75" s="18"/>
-      <c r="K75" s="18"/>
-      <c r="L75" s="18"/>
-      <c r="M75" s="18"/>
-      <c r="N75" s="18"/>
-      <c r="O75" s="18"/>
-      <c r="P75" s="18"/>
-      <c r="Q75" s="18"/>
+        <v>178</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="19"/>
+      <c r="M75" s="19"/>
+      <c r="N75" s="19"/>
+      <c r="O75" s="19"/>
+      <c r="P75" s="19"/>
+      <c r="Q75" s="19"/>
     </row>
     <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B76" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="18"/>
-      <c r="H76" s="18"/>
-      <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="18"/>
-      <c r="M76" s="18"/>
-      <c r="N76" s="18"/>
-      <c r="O76" s="18"/>
-      <c r="P76" s="18"/>
-      <c r="Q76" s="18"/>
+        <v>179</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
+      <c r="L76" s="19"/>
+      <c r="M76" s="19"/>
+      <c r="N76" s="19"/>
+      <c r="O76" s="19"/>
+      <c r="P76" s="19"/>
+      <c r="Q76" s="19"/>
     </row>
     <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B77" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="B77" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="18"/>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="18"/>
-      <c r="M77" s="18"/>
-      <c r="N77" s="18"/>
-      <c r="O77" s="18"/>
-      <c r="P77" s="18"/>
-      <c r="Q77" s="18"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19"/>
+      <c r="K77" s="19"/>
+      <c r="L77" s="19"/>
+      <c r="M77" s="19"/>
+      <c r="N77" s="19"/>
+      <c r="O77" s="19"/>
+      <c r="P77" s="19"/>
+      <c r="Q77" s="19"/>
     </row>
     <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B78" s="21"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
+      <c r="A78" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -4904,11 +4905,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="20">
-    <mergeCell ref="B61:Q61"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:Q71"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="B73:Q73"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="B64:Q64"/>
@@ -4924,6 +4920,11 @@
     <mergeCell ref="B70:Q70"/>
     <mergeCell ref="B76:Q76"/>
     <mergeCell ref="B77:Q77"/>
+    <mergeCell ref="B61:Q61"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:Q71"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="B73:Q73"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4940,10 +4941,10 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -4951,26 +4952,26 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12">
         <v>18.75</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H12" s="25"/>
       <c r="J12" s="25"/>
@@ -4978,19 +4979,19 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" t="s">
         <v>132</v>
       </c>
-      <c r="D13" t="s">
-        <v>133</v>
-      </c>
       <c r="E13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" t="s">
         <v>140</v>
-      </c>
-      <c r="H13" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -5006,7 +5007,7 @@
         <v>18.75</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5025,7 +5026,7 @@
         <v>18.75</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -5044,7 +5045,7 @@
         <v>18.75</v>
       </c>
       <c r="G16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -5063,7 +5064,7 @@
         <v>18.75</v>
       </c>
       <c r="G17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -5082,7 +5083,7 @@
         <v>18.75</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H18">
         <v>0</v>

--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B989E7C-DFE7-43F1-BAC4-D636769015C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B8733F-4BFD-42F6-B3C1-E7720A81C02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="2190" windowWidth="16365" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色列表" sheetId="1" r:id="rId1"/>
-    <sheet name="平衡调整" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="平衡调整" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">角色列表!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">角色列表!$A$1:$Q$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,14 +30,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="205">
   <si>
     <t>No.</t>
   </si>
   <si>
-    <t>等级</t>
-  </si>
-  <si>
     <t>名称</t>
   </si>
   <si>
@@ -64,9 +62,6 @@
     <t>协同英雄</t>
   </si>
   <si>
-    <t>白</t>
-  </si>
-  <si>
     <t>伐木工</t>
   </si>
   <si>
@@ -163,9 +158,6 @@
     <t>独脚龟</t>
   </si>
   <si>
-    <t>金</t>
-  </si>
-  <si>
     <t>古拉博士</t>
   </si>
   <si>
@@ -268,9 +260,6 @@
     <t>移动后，令相邻敌人获得[冰冻]。</t>
   </si>
   <si>
-    <t>紫</t>
-  </si>
-  <si>
     <t>暗域</t>
   </si>
   <si>
@@ -322,9 +311,6 @@
     <t>远程攻击后，目标获得[沉默]。</t>
   </si>
   <si>
-    <t>炸弹人</t>
-  </si>
-  <si>
     <t>移动后，正前方（面对敌方底线方向）如果是空地，则放置一颗炸弹。炸弹人以外的角色如果停留在该格就会引爆，受到5点伤害。</t>
   </si>
   <si>
@@ -332,9 +318,6 @@
   </si>
   <si>
     <t>随机令HP最低的队友之一回复8点HP，然后与其交换位置。</t>
-  </si>
-  <si>
-    <t>虹</t>
   </si>
   <si>
     <t>锤头鲨</t>
@@ -1596,6 +1579,54 @@
   </si>
   <si>
     <t>对方回合结束时，随机变为己方队伍中的一名其他角色，暂时获得其所有技能和特性，直到下次变化为止。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人族</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兽族</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔族</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人族</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>种族</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔族</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兽族</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸弹人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2164,64 +2195,64 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="M1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="P1" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>150</v>
-      </c>
       <c r="Q1" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>11</v>
+      <c r="B2" t="s">
+        <v>198</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" s="7">
         <v>3</v>
@@ -2231,10 +2262,10 @@
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -2264,11 +2295,11 @@
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>11</v>
+      <c r="B3" t="s">
+        <v>198</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" s="9">
         <v>2</v>
@@ -2277,13 +2308,13 @@
         <v>24</v>
       </c>
       <c r="F3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>18</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -2313,11 +2344,11 @@
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>11</v>
+      <c r="B4" t="s">
+        <v>202</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" s="7">
         <v>1</v>
@@ -2327,14 +2358,14 @@
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="3">
@@ -2362,11 +2393,11 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>11</v>
+      <c r="B5" t="s">
+        <v>202</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" s="9">
         <v>4</v>
@@ -2375,7 +2406,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -2407,11 +2438,11 @@
       <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>11</v>
+      <c r="B6" t="s">
+        <v>200</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="7">
         <v>3</v>
@@ -2420,13 +2451,13 @@
         <v>19</v>
       </c>
       <c r="F6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -2456,11 +2487,11 @@
       <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>11</v>
+      <c r="B7" t="s">
+        <v>198</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" s="9">
         <v>3</v>
@@ -2469,13 +2500,13 @@
         <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -2505,11 +2536,11 @@
       <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>11</v>
+      <c r="B8" t="s">
+        <v>198</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" s="7">
         <v>5</v>
@@ -2518,11 +2549,11 @@
         <v>14</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -2550,11 +2581,11 @@
       <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>11</v>
+      <c r="B9" t="s">
+        <v>201</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D9" s="9">
         <v>2</v>
@@ -2563,13 +2594,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -2599,11 +2630,11 @@
       <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>11</v>
+      <c r="B10" t="s">
+        <v>198</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="7">
         <v>4</v>
@@ -2612,7 +2643,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
@@ -2642,11 +2673,11 @@
       <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>11</v>
+      <c r="B11" t="s">
+        <v>201</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
@@ -2655,13 +2686,13 @@
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -2691,11 +2722,11 @@
       <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>11</v>
+      <c r="B12" t="s">
+        <v>198</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="7">
         <v>1</v>
@@ -2704,10 +2735,10 @@
         <v>40</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -2738,11 +2769,11 @@
       <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>11</v>
+      <c r="B13" t="s">
+        <v>198</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" s="9">
         <v>2</v>
@@ -2751,10 +2782,10 @@
         <v>24</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -2785,11 +2816,11 @@
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>11</v>
+      <c r="B14" t="s">
+        <v>202</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" s="7">
         <v>2</v>
@@ -2798,7 +2829,7 @@
         <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -2830,11 +2861,11 @@
       <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>44</v>
+      <c r="B15" t="s">
+        <v>200</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D15" s="9">
         <v>4</v>
@@ -2844,10 +2875,10 @@
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
@@ -2877,11 +2908,11 @@
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>44</v>
+      <c r="B16" t="s">
+        <v>200</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="7">
         <v>3</v>
@@ -2890,13 +2921,13 @@
         <v>18</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
@@ -2926,11 +2957,11 @@
       <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>44</v>
+      <c r="B17" t="s">
+        <v>203</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D17" s="9">
         <v>4</v>
@@ -2939,10 +2970,10 @@
         <v>16</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -2973,11 +3004,11 @@
       <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>44</v>
+      <c r="B18" t="s">
+        <v>201</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18" s="7">
         <v>3</v>
@@ -2986,13 +3017,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -3022,11 +3053,11 @@
       <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>44</v>
+      <c r="B19" t="s">
+        <v>198</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D19" s="9">
         <v>3</v>
@@ -3035,13 +3066,13 @@
         <v>18</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
@@ -3071,11 +3102,11 @@
       <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>44</v>
+      <c r="B20" t="s">
+        <v>198</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D20" s="7">
         <v>1</v>
@@ -3084,13 +3115,13 @@
         <v>18</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
@@ -3120,11 +3151,11 @@
       <c r="A21" s="9">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>44</v>
+      <c r="B21" t="s">
+        <v>198</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D21" s="9">
         <v>3</v>
@@ -3134,13 +3165,13 @@
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -3169,11 +3200,11 @@
       <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>44</v>
+      <c r="B22" t="s">
+        <v>201</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D22" s="7">
         <v>3</v>
@@ -3182,13 +3213,13 @@
         <v>19</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
@@ -3218,11 +3249,11 @@
       <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>44</v>
+      <c r="B23" t="s">
+        <v>201</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D23" s="9">
         <v>2</v>
@@ -3231,10 +3262,10 @@
         <v>18</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -3267,11 +3298,11 @@
       <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>44</v>
+      <c r="B24" t="s">
+        <v>198</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D24" s="7">
         <v>2</v>
@@ -3280,10 +3311,10 @@
         <v>26</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -3314,11 +3345,11 @@
       <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>44</v>
+      <c r="B25" t="s">
+        <v>198</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D25" s="9">
         <v>2</v>
@@ -3327,10 +3358,10 @@
         <v>21</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -3361,11 +3392,11 @@
       <c r="A26" s="7">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>44</v>
+      <c r="B26" t="s">
+        <v>198</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D26" s="7">
         <v>2</v>
@@ -3374,14 +3405,14 @@
         <v>24</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -3410,11 +3441,11 @@
       <c r="A27" s="9">
         <v>26</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>44</v>
+      <c r="B27" t="s">
+        <v>198</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D27" s="9">
         <v>2</v>
@@ -3423,10 +3454,10 @@
         <v>26</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -3457,11 +3488,11 @@
       <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>79</v>
+      <c r="B28" t="s">
+        <v>200</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D28" s="7">
         <v>3</v>
@@ -3470,13 +3501,13 @@
         <v>20</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
@@ -3506,11 +3537,11 @@
       <c r="A29" s="9">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>79</v>
+      <c r="B29" t="s">
+        <v>201</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D29" s="9">
         <v>3</v>
@@ -3520,10 +3551,10 @@
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="13" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
@@ -3553,11 +3584,11 @@
       <c r="A30" s="7">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>79</v>
+      <c r="B30" t="s">
+        <v>198</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D30" s="7">
         <v>3</v>
@@ -3566,10 +3597,10 @@
         <v>16</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -3600,11 +3631,11 @@
       <c r="A31" s="9">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="D31" s="9">
         <v>3</v>
@@ -3614,10 +3645,10 @@
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -3647,11 +3678,11 @@
       <c r="A32" s="7">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>79</v>
+      <c r="B32" t="s">
+        <v>200</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D32" s="7">
         <v>3</v>
@@ -3660,10 +3691,10 @@
         <v>18</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -3694,11 +3725,11 @@
       <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>79</v>
+      <c r="B33" t="s">
+        <v>202</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D33" s="9">
         <v>2</v>
@@ -3708,10 +3739,10 @@
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="9"/>
@@ -3741,11 +3772,11 @@
       <c r="A34" s="7">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>79</v>
+      <c r="B34" t="s">
+        <v>200</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D34" s="7">
         <v>1</v>
@@ -3754,13 +3785,13 @@
         <v>18</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -3790,11 +3821,11 @@
       <c r="A35" s="9">
         <v>34</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>79</v>
+      <c r="B35" t="s">
+        <v>200</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D35" s="9">
         <v>3</v>
@@ -3803,16 +3834,16 @@
         <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -3841,11 +3872,11 @@
       <c r="A36" s="7">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>97</v>
+      <c r="B36" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>204</v>
       </c>
       <c r="D36" s="7">
         <v>3</v>
@@ -3854,13 +3885,13 @@
         <v>20</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
@@ -3890,11 +3921,11 @@
       <c r="A37" s="9">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>79</v>
+      <c r="B37" t="s">
+        <v>203</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D37" s="9">
         <v>2</v>
@@ -3903,10 +3934,10 @@
         <v>20</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -3937,11 +3968,11 @@
       <c r="A38" s="7">
         <v>37</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>101</v>
+      <c r="B38" t="s">
+        <v>202</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D38" s="7">
         <v>2</v>
@@ -3951,10 +3982,10 @@
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
@@ -3984,11 +4015,11 @@
       <c r="A39" s="9">
         <v>38</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>101</v>
+      <c r="B39" t="s">
+        <v>203</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D39" s="9">
         <v>0</v>
@@ -3997,10 +4028,10 @@
         <v>27</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -4031,11 +4062,11 @@
       <c r="A40" s="7">
         <v>39</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>101</v>
+      <c r="B40" t="s">
+        <v>202</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D40" s="7">
         <v>3</v>
@@ -4044,10 +4075,10 @@
         <v>17</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
@@ -4078,11 +4109,11 @@
       <c r="A41" s="9">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>101</v>
+      <c r="B41" t="s">
+        <v>198</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D41" s="9">
         <v>5</v>
@@ -4092,7 +4123,7 @@
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -4123,11 +4154,11 @@
       <c r="A42" s="7">
         <v>41</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>101</v>
+      <c r="B42" t="s">
+        <v>200</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D42" s="7">
         <v>2</v>
@@ -4137,10 +4168,10 @@
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
@@ -4170,11 +4201,11 @@
       <c r="A43" s="9">
         <v>42</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>101</v>
+      <c r="B43" t="s">
+        <v>198</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D43" s="9">
         <v>2</v>
@@ -4183,10 +4214,10 @@
         <v>18</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -4217,11 +4248,11 @@
       <c r="A44" s="7">
         <v>43</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>101</v>
+      <c r="B44" t="s">
+        <v>201</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D44" s="7">
         <v>1</v>
@@ -4230,10 +4261,10 @@
         <v>14</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -4266,11 +4297,11 @@
       <c r="A45" s="9">
         <v>44</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>79</v>
+      <c r="B45" t="s">
+        <v>200</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D45" s="9">
         <v>2</v>
@@ -4279,14 +4310,14 @@
         <v>26</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
@@ -4315,11 +4346,11 @@
       <c r="A46" s="7">
         <v>45</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>44</v>
+      <c r="B46" t="s">
+        <v>198</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D46" s="7">
         <v>3</v>
@@ -4328,10 +4359,10 @@
         <v>16</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
@@ -4362,11 +4393,11 @@
       <c r="A47" s="9">
         <v>46</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>79</v>
+      <c r="B47" t="s">
+        <v>200</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D47" s="9">
         <v>2</v>
@@ -4375,14 +4406,14 @@
         <v>19</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="12" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
@@ -4411,11 +4442,11 @@
       <c r="A48" s="7">
         <v>47</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>79</v>
+      <c r="B48" t="s">
+        <v>201</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D48" s="7">
         <v>0</v>
@@ -4424,13 +4455,13 @@
         <v>18</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
@@ -4458,13 +4489,13 @@
     </row>
     <row r="49" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -4474,7 +4505,7 @@
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="9" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
@@ -4495,7 +4526,7 @@
     </row>
     <row r="58" spans="1:17" ht="27" x14ac:dyDescent="0.2">
       <c r="A58" s="20" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
@@ -4505,7 +4536,7 @@
     </row>
     <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="21" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
@@ -4515,10 +4546,10 @@
     </row>
     <row r="60" spans="1:17" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C60" s="24"/>
       <c r="D60" s="24"/>
@@ -4527,10 +4558,10 @@
     </row>
     <row r="61" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A61" s="17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C61" s="18"/>
       <c r="D61" s="18"/>
@@ -4550,10 +4581,10 @@
     </row>
     <row r="62" spans="1:17" ht="18" x14ac:dyDescent="0.2">
       <c r="A62" s="16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
@@ -4573,10 +4604,10 @@
     </row>
     <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
@@ -4596,10 +4627,10 @@
     </row>
     <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
@@ -4619,10 +4650,10 @@
     </row>
     <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
@@ -4642,10 +4673,10 @@
     </row>
     <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
@@ -4673,7 +4704,7 @@
     </row>
     <row r="68" spans="1:17" ht="27" x14ac:dyDescent="0.2">
       <c r="A68" s="23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -4683,10 +4714,10 @@
     </row>
     <row r="69" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A69" s="17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
@@ -4706,10 +4737,10 @@
     </row>
     <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="16" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
@@ -4729,10 +4760,10 @@
     </row>
     <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
@@ -4752,10 +4783,10 @@
     </row>
     <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
@@ -4775,10 +4806,10 @@
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="16" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
@@ -4798,10 +4829,10 @@
     </row>
     <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" s="19" t="s">
         <v>177</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>183</v>
       </c>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
@@ -4821,10 +4852,10 @@
     </row>
     <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
@@ -4844,10 +4875,10 @@
     </row>
     <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="16" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
@@ -4867,10 +4898,10 @@
     </row>
     <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
@@ -4890,7 +4921,7 @@
     </row>
     <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="22" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
@@ -4899,7 +4930,7 @@
       <c r="F78" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:Q49" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q49">
       <sortCondition ref="A1"/>
     </sortState>
@@ -4932,6 +4963,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADD8E7B9-04EA-4D55-84C7-0A81666BDF39}">
+  <dimension ref="C12:C16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="12" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF6EE44-8C24-409F-B95B-366E700D4059}">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4941,10 +5008,10 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -4952,26 +5019,26 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E12">
         <v>18.75</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H12" s="25"/>
       <c r="J12" s="25"/>
@@ -4979,19 +5046,19 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -5007,7 +5074,7 @@
         <v>18.75</v>
       </c>
       <c r="G14" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5026,7 +5093,7 @@
         <v>18.75</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -5045,7 +5112,7 @@
         <v>18.75</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -5064,7 +5131,7 @@
         <v>18.75</v>
       </c>
       <c r="G17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -5083,7 +5150,7 @@
         <v>18.75</v>
       </c>
       <c r="G18" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H18">
         <v>0</v>

--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FC6DD0-C6C8-4E37-BA91-9FF83BCEC3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14845537-D945-4562-B8C4-AE413542DE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,9 +219,6 @@
     <t>圣光</t>
   </si>
   <si>
-    <t>每回合限一次，一名己方角色受伤后，其获得[圣盾]。</t>
-  </si>
-  <si>
     <t>复仇者</t>
   </si>
   <si>
@@ -2269,6 +2266,10 @@
   </si>
   <si>
     <t>装甲堡垒在我方回合没有移动时，装甲堡垒获得[坚固]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌方回合，一名己方英雄受到伤害后，其获得[圣盾]，一回合限一次。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2526,18 +2527,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2574,9 +2563,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2589,11 +2575,32 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2601,14 +2608,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2893,1799 +2894,1799 @@
   <dimension ref="A1:R52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="11"/>
-    <col min="3" max="3" width="9.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="34.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.25" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="10.5" style="11" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="8" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="7"/>
+    <col min="3" max="3" width="9.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9" style="7"/>
+    <col min="7" max="7" width="34.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="9" style="7"/>
+    <col min="14" max="14" width="10.5" style="7" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="R1" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A2" s="9">
+        <v>27</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="17" t="s">
+      <c r="C2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="9">
         <v>3</v>
       </c>
-      <c r="F1" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="O1" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q1" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="R1" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="13">
-        <v>27</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="9">
+        <v>20</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="13">
+      <c r="G2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="10">
+        <f t="shared" ref="L2:L33" si="0">D2*2.2+E2*0.45</f>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="M2" s="10">
+        <f t="shared" ref="M2:M33" si="1">SUM(IF(ISNUMBER(SEARCH("疾行",F2)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F2)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F2)),-1,0), IF(ISNUMBER(SEARCH("后勤",F2)),1,0))</f>
         <v>3</v>
       </c>
-      <c r="E2" s="13">
-        <v>20</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="14">
-        <f>D2*2.2+E2*0.45</f>
-        <v>15.600000000000001</v>
-      </c>
-      <c r="M2" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F2)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F2)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F2)),-1,0), IF(ISNUMBER(SEARCH("后勤",F2)),1,0))</f>
-        <v>3</v>
-      </c>
-      <c r="N2" s="14">
+      <c r="N2" s="10">
         <v>1.5</v>
       </c>
-      <c r="O2" s="14">
+      <c r="O2" s="10">
         <f>N2*2.2</f>
         <v>3.3000000000000003</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14">
-        <f>L2+M2+O2+P2</f>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10">
+        <f t="shared" ref="Q2:Q33" si="2">L2+M2+O2+P2</f>
         <v>21.900000000000002</v>
       </c>
-      <c r="R2" s="14" t="s">
-        <v>169</v>
+      <c r="R2" s="10" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="57" x14ac:dyDescent="0.2">
-      <c r="A3" s="13">
+      <c r="A3" s="9">
         <v>34</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="9">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9">
+        <v>15</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="13">
+      <c r="H3" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="10">
+        <f t="shared" si="0"/>
+        <v>13.350000000000001</v>
+      </c>
+      <c r="M3" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N3" s="10">
         <v>3</v>
       </c>
-      <c r="E3" s="13">
-        <v>15</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="14">
-        <f>D3*2.2+E3*0.45</f>
-        <v>13.350000000000001</v>
-      </c>
-      <c r="M3" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F3)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F3)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F3)),-1,0), IF(ISNUMBER(SEARCH("后勤",F3)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N3" s="14">
-        <v>3</v>
-      </c>
-      <c r="O3" s="14">
+      <c r="O3" s="10">
         <f>N3*2.2</f>
         <v>6.6000000000000005</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14">
-        <f>L3+M3+O3+P3</f>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10">
+        <f t="shared" si="2"/>
         <v>21.450000000000003</v>
       </c>
-      <c r="R3" s="14" t="s">
+      <c r="R3" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="9">
+        <v>40</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="13">
-        <v>40</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C4" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="9">
         <v>5</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="9">
         <v>13</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14">
-        <f>D4*2.2+E4*0.45</f>
+      <c r="F4" s="9"/>
+      <c r="G4" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="10">
+        <f t="shared" si="0"/>
         <v>16.850000000000001</v>
       </c>
-      <c r="M4" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F4)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F4)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F4)),-1,0), IF(ISNUMBER(SEARCH("后勤",F4)),1,0))</f>
+      <c r="M4" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="10">
         <v>2</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="10">
         <f>N4*2.2</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14">
-        <f>L4+M4+O4+P4</f>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10">
+        <f t="shared" si="2"/>
         <v>21.25</v>
       </c>
-      <c r="R4" s="14" t="s">
-        <v>177</v>
+      <c r="R4" s="10" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="13">
+      <c r="A5" s="9">
         <v>17</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="9">
         <v>3</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="9">
         <v>17</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="14">
-        <f>D5*2.2+E5*0.45</f>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="10">
+        <f t="shared" si="0"/>
         <v>14.25</v>
       </c>
-      <c r="M5" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F5)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F5)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F5)),-1,0), IF(ISNUMBER(SEARCH("后勤",F5)),1,0))</f>
+      <c r="M5" s="10">
+        <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="10">
         <v>2</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="10">
         <f>N5*2.2</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14">
-        <f>L5+M5+O5+P5</f>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10">
+        <f t="shared" si="2"/>
         <v>21.15</v>
       </c>
-      <c r="R5" s="14" t="s">
-        <v>177</v>
+      <c r="R5" s="10" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="13">
+      <c r="A6" s="9">
         <v>22</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="9">
         <v>2</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="9">
         <v>18</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="14">
-        <f>D6*2.2+E6*0.45</f>
+      <c r="G6" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10">
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="M6" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F6)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F6)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F6)),-1,0), IF(ISNUMBER(SEARCH("后勤",F6)),1,0))</f>
+      <c r="M6" s="10">
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="10">
         <v>3</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="10">
         <f>N6*0.45</f>
         <v>1.35</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="10">
         <v>8</v>
       </c>
-      <c r="Q6" s="14">
-        <f>L6+M6+O6+P6</f>
+      <c r="Q6" s="10">
+        <f t="shared" si="2"/>
         <v>20.85</v>
       </c>
-      <c r="R6" s="14" t="s">
-        <v>178</v>
+      <c r="R6" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="13">
+      <c r="A7" s="9">
         <v>18</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="9">
         <v>3</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="9">
         <v>18</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="14">
-        <f>D7*2.2+E7*0.45</f>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="10">
+        <f t="shared" si="0"/>
         <v>14.7</v>
       </c>
-      <c r="M7" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F7)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F7)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F7)),-1,0), IF(ISNUMBER(SEARCH("后勤",F7)),1,0))</f>
+      <c r="M7" s="10">
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="10">
         <v>2</v>
       </c>
-      <c r="O7" s="14">
-        <f>N7*2.2</f>
+      <c r="O7" s="10">
+        <f t="shared" ref="O7:O22" si="3">N7*2.2</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14">
-        <f>L7+M7+O7+P7</f>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10">
+        <f t="shared" si="2"/>
         <v>20.6</v>
       </c>
-      <c r="R7" s="14" t="s">
+      <c r="R7" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="9">
+        <v>42</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="9">
+        <v>2</v>
+      </c>
+      <c r="E8" s="9">
+        <v>18</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="10">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="M8" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N8" s="10">
+        <v>3</v>
+      </c>
+      <c r="O8" s="10">
+        <f t="shared" si="3"/>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10">
+        <f t="shared" si="2"/>
+        <v>20.6</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="69" x14ac:dyDescent="0.2">
+      <c r="A9" s="9">
+        <v>30</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="9">
+        <v>3</v>
+      </c>
+      <c r="E9" s="9">
+        <v>20</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="10">
+        <f t="shared" si="0"/>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="M9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
+        <v>2</v>
+      </c>
+      <c r="O9" s="10">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <v>35</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="9">
+        <v>3</v>
+      </c>
+      <c r="E10" s="9">
+        <v>20</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="10">
+        <f t="shared" si="0"/>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="M10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="10">
+        <v>2</v>
+      </c>
+      <c r="O10" s="10">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="R10" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="9">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="9">
+        <v>3</v>
+      </c>
+      <c r="E11" s="9">
+        <v>19</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="10">
+        <f t="shared" si="0"/>
+        <v>15.150000000000002</v>
+      </c>
+      <c r="M11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="10">
+        <v>2</v>
+      </c>
+      <c r="O11" s="10">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10">
+        <f t="shared" si="2"/>
+        <v>19.550000000000004</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="9">
+        <v>15</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="9">
+        <v>3</v>
+      </c>
+      <c r="E12" s="9">
+        <v>18</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10">
+        <f t="shared" si="0"/>
+        <v>14.7</v>
+      </c>
+      <c r="M12" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N12" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="O12" s="10">
+        <f t="shared" si="3"/>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10">
+        <f t="shared" si="2"/>
+        <v>19.5</v>
+      </c>
+      <c r="R12" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="9">
+        <v>23</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="9">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9">
+        <v>26</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="10">
+        <f t="shared" si="0"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M13" s="10">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="N13" s="10">
+        <v>2</v>
+      </c>
+      <c r="O13" s="10">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10">
+        <f t="shared" si="2"/>
+        <v>19.5</v>
+      </c>
+      <c r="R13" s="10" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="13">
-        <v>42</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="13">
+    <row r="14" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+      <c r="A14" s="9">
+        <v>44</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="9">
         <v>2</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E14" s="9">
+        <v>26</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10">
+        <f t="shared" si="0"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M14" s="10">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="N14" s="10">
+        <v>2</v>
+      </c>
+      <c r="O14" s="10">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10">
+        <f t="shared" si="2"/>
+        <v>19.5</v>
+      </c>
+      <c r="R14" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A15" s="9">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="9">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9">
+        <v>40</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10">
+        <f t="shared" si="0"/>
+        <v>20.2</v>
+      </c>
+      <c r="M15" s="10">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10">
+        <f t="shared" si="2"/>
+        <v>19.2</v>
+      </c>
+      <c r="R15" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="9">
+        <v>28</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="9">
+        <v>3</v>
+      </c>
+      <c r="E16" s="9">
         <v>18</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F16" s="9"/>
+      <c r="G16" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="10">
+        <f t="shared" si="0"/>
+        <v>14.7</v>
+      </c>
+      <c r="M16" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="10">
+        <v>2</v>
+      </c>
+      <c r="O16" s="10">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10">
+        <f t="shared" si="2"/>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R16" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+      <c r="A17" s="9">
+        <v>2</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="9">
+        <v>2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>24</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="14">
-        <f>D8*2.2+E8*0.45</f>
-        <v>12.5</v>
-      </c>
-      <c r="M8" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F8)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F8)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F8)),-1,0), IF(ISNUMBER(SEARCH("后勤",F8)),1,0))</f>
+      <c r="G17" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="10">
+        <f t="shared" si="0"/>
+        <v>15.200000000000001</v>
+      </c>
+      <c r="M17" s="10">
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N17" s="10">
+        <v>1</v>
+      </c>
+      <c r="O17" s="10">
+        <f t="shared" si="3"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10">
+        <f t="shared" si="2"/>
+        <v>18.900000000000002</v>
+      </c>
+      <c r="R17" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="9">
+        <v>10</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="9">
+        <v>2</v>
+      </c>
+      <c r="E18" s="9">
+        <v>19</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="10">
+        <f t="shared" si="0"/>
+        <v>12.950000000000001</v>
+      </c>
+      <c r="M18" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N18" s="10">
+        <v>2</v>
+      </c>
+      <c r="O18" s="10">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10">
+        <f t="shared" si="2"/>
+        <v>18.850000000000001</v>
+      </c>
+      <c r="R18" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="9">
+        <v>46</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="9">
+        <v>2</v>
+      </c>
+      <c r="E19" s="9">
+        <v>19</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="10">
+        <f t="shared" si="0"/>
+        <v>12.950000000000001</v>
+      </c>
+      <c r="M19" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N19" s="10">
+        <v>2</v>
+      </c>
+      <c r="O19" s="10">
+        <f t="shared" si="3"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10">
+        <f t="shared" si="2"/>
+        <v>18.850000000000001</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="9">
+        <v>7</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="9">
+        <v>5</v>
+      </c>
+      <c r="E20" s="9">
+        <v>14</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="20"/>
+      <c r="H20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="10">
+        <f t="shared" si="0"/>
+        <v>17.3</v>
+      </c>
+      <c r="M20" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10">
+        <f t="shared" si="2"/>
+        <v>18.8</v>
+      </c>
+      <c r="R20" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="9">
+        <v>26</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="9">
+        <v>2</v>
+      </c>
+      <c r="E21" s="9">
+        <v>26</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="10">
+        <f t="shared" si="0"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="N21" s="10">
+        <v>1</v>
+      </c>
+      <c r="O21" s="10">
+        <f t="shared" si="3"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10">
+        <f t="shared" si="2"/>
+        <v>18.8</v>
+      </c>
+      <c r="R21" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="9">
+        <v>1</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="9">
         <v>3</v>
       </c>
-      <c r="O8" s="14">
-        <f>N8*2.2</f>
-        <v>6.6000000000000005</v>
-      </c>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14">
-        <f>L8+M8+O8+P8</f>
-        <v>20.6</v>
-      </c>
-      <c r="R8" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="69" x14ac:dyDescent="0.2">
-      <c r="A9" s="13">
-        <v>30</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="13">
+      <c r="E22" s="9">
+        <v>27</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="10">
+        <f t="shared" si="0"/>
+        <v>18.75</v>
+      </c>
+      <c r="M22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10">
+        <f t="shared" si="2"/>
+        <v>18.75</v>
+      </c>
+      <c r="R22" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="9">
+        <v>48</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="9">
+        <v>1</v>
+      </c>
+      <c r="E23" s="9">
+        <v>36</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="10">
+        <f t="shared" si="0"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="M23" s="10">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="N23" s="10">
         <v>3</v>
       </c>
-      <c r="E9" s="13">
-        <v>20</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="14">
-        <f>D9*2.2+E9*0.45</f>
-        <v>15.600000000000001</v>
-      </c>
-      <c r="M9" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F9)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F9)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F9)),-1,0), IF(ISNUMBER(SEARCH("后勤",F9)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="14">
-        <v>2</v>
-      </c>
-      <c r="O9" s="14">
-        <f>N9*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14">
-        <f>L9+M9+O9+P9</f>
-        <v>20</v>
-      </c>
-      <c r="R9" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="13">
-        <v>35</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="13">
-        <v>3</v>
-      </c>
-      <c r="E10" s="13">
-        <v>20</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="14">
-        <f>D10*2.2+E10*0.45</f>
-        <v>15.600000000000001</v>
-      </c>
-      <c r="M10" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F10)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F10)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F10)),-1,0), IF(ISNUMBER(SEARCH("后勤",F10)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="14">
-        <v>2</v>
-      </c>
-      <c r="O10" s="14">
-        <f>N10*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14">
-        <f>L10+M10+O10+P10</f>
-        <v>20</v>
-      </c>
-      <c r="R10" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="13">
-        <v>20</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="13">
-        <v>3</v>
-      </c>
-      <c r="E11" s="13">
-        <v>19</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="14">
-        <f>D11*2.2+E11*0.45</f>
-        <v>15.150000000000002</v>
-      </c>
-      <c r="M11" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F11)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F11)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F11)),-1,0), IF(ISNUMBER(SEARCH("后勤",F11)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="14">
-        <v>2</v>
-      </c>
-      <c r="O11" s="14">
-        <f>N11*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14">
-        <f>L11+M11+O11+P11</f>
-        <v>19.550000000000004</v>
-      </c>
-      <c r="R11" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A12" s="13">
-        <v>15</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="13">
-        <v>3</v>
-      </c>
-      <c r="E12" s="13">
-        <v>18</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="14">
-        <f>D12*2.2+E12*0.45</f>
-        <v>14.7</v>
-      </c>
-      <c r="M12" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F12)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F12)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F12)),-1,0), IF(ISNUMBER(SEARCH("后勤",F12)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N12" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="O12" s="14">
-        <f>N12*2.2</f>
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14">
-        <f>L12+M12+O12+P12</f>
-        <v>19.5</v>
-      </c>
-      <c r="R12" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="13">
-        <v>23</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="13">
-        <v>2</v>
-      </c>
-      <c r="E13" s="13">
-        <v>26</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="14">
-        <f>D13*2.2+E13*0.45</f>
-        <v>16.100000000000001</v>
-      </c>
-      <c r="M13" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F13)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F13)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F13)),-1,0), IF(ISNUMBER(SEARCH("后勤",F13)),1,0))</f>
-        <v>-1</v>
-      </c>
-      <c r="N13" s="14">
-        <v>2</v>
-      </c>
-      <c r="O13" s="14">
-        <f>N13*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14">
-        <f>L13+M13+O13+P13</f>
-        <v>19.5</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="13">
-        <v>44</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="13">
-        <v>2</v>
-      </c>
-      <c r="E14" s="13">
-        <v>26</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="14">
-        <f>D14*2.2+E14*0.45</f>
-        <v>16.100000000000001</v>
-      </c>
-      <c r="M14" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F14)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F14)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F14)),-1,0), IF(ISNUMBER(SEARCH("后勤",F14)),1,0))</f>
-        <v>-1</v>
-      </c>
-      <c r="N14" s="14">
-        <v>2</v>
-      </c>
-      <c r="O14" s="14">
-        <f>N14*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14">
-        <f>L14+M14+O14+P14</f>
-        <v>19.5</v>
-      </c>
-      <c r="R14" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="13">
-        <v>11</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="13">
-        <v>1</v>
-      </c>
-      <c r="E15" s="13">
-        <v>40</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="14">
-        <f>D15*2.2+E15*0.45</f>
-        <v>20.2</v>
-      </c>
-      <c r="M15" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F15)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F15)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F15)),-1,0), IF(ISNUMBER(SEARCH("后勤",F15)),1,0))</f>
-        <v>-1</v>
-      </c>
-      <c r="N15" s="14">
-        <v>0</v>
-      </c>
-      <c r="O15" s="14">
-        <f>N15*2.2</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14">
-        <f>L15+M15+O15+P15</f>
-        <v>19.2</v>
-      </c>
-      <c r="R15" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="13">
-        <v>28</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="13">
-        <v>3</v>
-      </c>
-      <c r="E16" s="13">
-        <v>18</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="14">
-        <f>D16*2.2+E16*0.45</f>
-        <v>14.7</v>
-      </c>
-      <c r="M16" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F16)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F16)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F16)),-1,0), IF(ISNUMBER(SEARCH("后勤",F16)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="14">
-        <v>2</v>
-      </c>
-      <c r="O16" s="14">
-        <f>N16*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14">
-        <f>L16+M16+O16+P16</f>
-        <v>19.100000000000001</v>
-      </c>
-      <c r="R16" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" s="13">
-        <v>2</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="13">
-        <v>2</v>
-      </c>
-      <c r="E17" s="13">
-        <v>24</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="14">
-        <f>D17*2.2+E17*0.45</f>
-        <v>15.200000000000001</v>
-      </c>
-      <c r="M17" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F17)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F17)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F17)),-1,0), IF(ISNUMBER(SEARCH("后勤",F17)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N17" s="14">
-        <v>1</v>
-      </c>
-      <c r="O17" s="14">
-        <f>N17*2.2</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14">
-        <f>L17+M17+O17+P17</f>
-        <v>18.900000000000002</v>
-      </c>
-      <c r="R17" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="13">
-        <v>10</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="13">
-        <v>2</v>
-      </c>
-      <c r="E18" s="13">
-        <v>19</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="14">
-        <f>D18*2.2+E18*0.45</f>
-        <v>12.950000000000001</v>
-      </c>
-      <c r="M18" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F18)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F18)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F18)),-1,0), IF(ISNUMBER(SEARCH("后勤",F18)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N18" s="14">
-        <v>2</v>
-      </c>
-      <c r="O18" s="14">
-        <f>N18*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14">
-        <f>L18+M18+O18+P18</f>
-        <v>18.850000000000001</v>
-      </c>
-      <c r="R18" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="13">
-        <v>46</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="13">
-        <v>2</v>
-      </c>
-      <c r="E19" s="13">
-        <v>19</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="14">
-        <f>D19*2.2+E19*0.45</f>
-        <v>12.950000000000001</v>
-      </c>
-      <c r="M19" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F19)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F19)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F19)),-1,0), IF(ISNUMBER(SEARCH("后勤",F19)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N19" s="14">
-        <v>2</v>
-      </c>
-      <c r="O19" s="14">
-        <f>N19*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14">
-        <f>L19+M19+O19+P19</f>
-        <v>18.850000000000001</v>
-      </c>
-      <c r="R19" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="13">
-        <v>7</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="13">
-        <v>5</v>
-      </c>
-      <c r="E20" s="13">
-        <v>14</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G20" s="25"/>
-      <c r="H20" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="14">
-        <f>D20*2.2+E20*0.45</f>
-        <v>17.3</v>
-      </c>
-      <c r="M20" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F20)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F20)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F20)),-1,0), IF(ISNUMBER(SEARCH("后勤",F20)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14">
-        <f>N20*2.2</f>
-        <v>0</v>
-      </c>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14">
-        <f>L20+M20+O20+P20</f>
-        <v>18.8</v>
-      </c>
-      <c r="R20" s="14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="13">
-        <v>26</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="13">
-        <v>2</v>
-      </c>
-      <c r="E21" s="13">
-        <v>26</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="14">
-        <f>D21*2.2+E21*0.45</f>
-        <v>16.100000000000001</v>
-      </c>
-      <c r="M21" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F21)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F21)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F21)),-1,0), IF(ISNUMBER(SEARCH("后勤",F21)),1,0))</f>
-        <v>0.5</v>
-      </c>
-      <c r="N21" s="14">
-        <v>1</v>
-      </c>
-      <c r="O21" s="14">
-        <f>N21*2.2</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14">
-        <f>L21+M21+O21+P21</f>
-        <v>18.8</v>
-      </c>
-      <c r="R21" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="13">
-        <v>1</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="13">
-        <v>3</v>
-      </c>
-      <c r="E22" s="13">
-        <v>27</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="14">
-        <f>D22*2.2+E22*0.45</f>
-        <v>18.75</v>
-      </c>
-      <c r="M22" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F22)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F22)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F22)),-1,0), IF(ISNUMBER(SEARCH("后勤",F22)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="14">
-        <v>0</v>
-      </c>
-      <c r="O22" s="14">
-        <f>N22*2.2</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14">
-        <f>L22+M22+O22+P22</f>
-        <v>18.75</v>
-      </c>
-      <c r="R22" s="14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="13">
-        <v>48</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="13">
-        <v>1</v>
-      </c>
-      <c r="E23" s="13">
-        <v>36</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="14">
-        <f>D23*2.2+E23*0.45</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="M23" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F23)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F23)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F23)),-1,0), IF(ISNUMBER(SEARCH("后勤",F23)),1,0))</f>
-        <v>-1</v>
-      </c>
-      <c r="N23" s="14">
-        <v>3</v>
-      </c>
-      <c r="O23" s="14">
+      <c r="O23" s="10">
         <f>N23*0.45</f>
         <v>1.35</v>
       </c>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14">
-        <f>L23+M23+O23+P23</f>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10">
+        <f t="shared" si="2"/>
         <v>18.75</v>
       </c>
-      <c r="R23" s="14" t="s">
-        <v>178</v>
+      <c r="R23" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="13">
+      <c r="A24" s="9">
         <v>16</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="13" t="s">
+      <c r="B24" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="9">
         <v>4</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="9">
         <v>16</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="14">
-        <f>D24*2.2+E24*0.45</f>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="10">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="M24" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F24)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F24)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F24)),-1,0), IF(ISNUMBER(SEARCH("后勤",F24)),1,0))</f>
+      <c r="M24" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N24" s="14">
+      <c r="N24" s="10">
         <v>6</v>
       </c>
-      <c r="O24" s="14">
+      <c r="O24" s="10">
         <f>N24*0.45</f>
         <v>2.7</v>
       </c>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14">
-        <f>L24+M24+O24+P24</f>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10">
+        <f t="shared" si="2"/>
         <v>18.7</v>
       </c>
-      <c r="R24" s="14" t="s">
+      <c r="R24" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A25" s="9">
+        <v>39</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="9">
+        <v>3</v>
+      </c>
+      <c r="E25" s="9">
+        <v>17</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="10">
+        <f t="shared" si="0"/>
+        <v>14.25</v>
+      </c>
+      <c r="M25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="10">
+        <v>2</v>
+      </c>
+      <c r="O25" s="10">
+        <f t="shared" ref="O25:O35" si="4">N25*2.2</f>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10">
+        <f t="shared" si="2"/>
+        <v>18.649999999999999</v>
+      </c>
+      <c r="R25" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="9">
+        <v>12</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="13">
+      <c r="C26" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="9">
+        <v>2</v>
+      </c>
+      <c r="E26" s="9">
+        <v>24</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="10">
+        <f t="shared" si="0"/>
+        <v>15.200000000000001</v>
+      </c>
+      <c r="M26" s="10">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="N26" s="10">
+        <v>2</v>
+      </c>
+      <c r="O26" s="10">
+        <f t="shared" si="4"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10">
+        <f t="shared" si="2"/>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="R26" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="9">
+        <v>25</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="9">
+        <v>2</v>
+      </c>
+      <c r="E27" s="9">
+        <v>24</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="10">
+        <f t="shared" si="0"/>
+        <v>15.200000000000001</v>
+      </c>
+      <c r="M27" s="10">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="N27" s="10">
+        <v>2</v>
+      </c>
+      <c r="O27" s="10">
+        <f t="shared" si="4"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10">
+        <f t="shared" si="2"/>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="R27" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="9">
+        <v>29</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="9">
+        <v>3</v>
+      </c>
+      <c r="E28" s="9">
+        <v>16</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="10">
+        <f t="shared" si="0"/>
+        <v>13.8</v>
+      </c>
+      <c r="M28" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N28" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="O28" s="10">
+        <f t="shared" si="4"/>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10">
+        <f t="shared" si="2"/>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="R28" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A29" s="9">
+        <v>32</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="9">
+        <v>2</v>
+      </c>
+      <c r="E29" s="9">
+        <v>24</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="10">
+        <f t="shared" si="0"/>
+        <v>15.200000000000001</v>
+      </c>
+      <c r="M29" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="O29" s="10">
+        <f t="shared" si="4"/>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10">
+        <f t="shared" si="2"/>
+        <v>18.5</v>
+      </c>
+      <c r="R29" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>21</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="9">
+        <v>3</v>
+      </c>
+      <c r="E30" s="9">
+        <v>19</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="10">
+        <f t="shared" si="0"/>
+        <v>15.150000000000002</v>
+      </c>
+      <c r="M30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="O30" s="10">
+        <f t="shared" si="4"/>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10">
+        <f t="shared" si="2"/>
+        <v>18.450000000000003</v>
+      </c>
+      <c r="R30" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="9">
+        <v>4</v>
+      </c>
+      <c r="E31" s="9">
+        <v>18</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="10">
+        <f t="shared" si="0"/>
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M31" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N31" s="10">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10">
+        <f t="shared" si="2"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="R31" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>47</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>18</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="10">
+        <f t="shared" si="0"/>
+        <v>8.1</v>
+      </c>
+      <c r="M32" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="N32" s="10">
+        <v>4</v>
+      </c>
+      <c r="O32" s="10">
+        <f t="shared" si="4"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10">
+        <f t="shared" si="2"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="R32" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>3</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="9">
+        <v>1</v>
+      </c>
+      <c r="E33" s="9">
+        <v>21</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="9"/>
+      <c r="I33" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="K33" s="9"/>
+      <c r="L33" s="10">
+        <f t="shared" si="0"/>
+        <v>11.650000000000002</v>
+      </c>
+      <c r="M33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="10">
+        <v>3</v>
+      </c>
+      <c r="O33" s="10">
+        <f t="shared" si="4"/>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10">
+        <f t="shared" si="2"/>
+        <v>18.250000000000004</v>
+      </c>
+      <c r="R33" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>13</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="13">
+      <c r="D34" s="9">
+        <v>2</v>
+      </c>
+      <c r="E34" s="9">
+        <v>33</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="20"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="10">
+        <f t="shared" ref="L34:L50" si="5">D34*2.2+E34*0.45</f>
+        <v>19.25</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" ref="M34:M50" si="6">SUM(IF(ISNUMBER(SEARCH("疾行",F34)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F34)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F34)),-1,0), IF(ISNUMBER(SEARCH("后勤",F34)),1,0))</f>
+        <v>-1</v>
+      </c>
+      <c r="N34" s="10">
+        <v>0</v>
+      </c>
+      <c r="O34" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10">
+        <f t="shared" ref="Q34:Q50" si="7">L34+M34+O34+P34</f>
+        <v>18.25</v>
+      </c>
+      <c r="R34" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="60" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>45</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" s="9">
         <v>3</v>
       </c>
-      <c r="E25" s="13">
-        <v>17</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="14">
-        <f>D25*2.2+E25*0.45</f>
-        <v>14.25</v>
-      </c>
-      <c r="M25" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F25)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F25)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F25)),-1,0), IF(ISNUMBER(SEARCH("后勤",F25)),1,0))</f>
+      <c r="E35" s="9">
+        <v>16</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="10">
+        <f t="shared" si="5"/>
+        <v>13.8</v>
+      </c>
+      <c r="M35" s="10">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N25" s="14">
+      <c r="N35" s="10">
         <v>2</v>
       </c>
-      <c r="O25" s="14">
-        <f>N25*2.2</f>
+      <c r="O35" s="10">
+        <f t="shared" si="4"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14">
-        <f>L25+M25+O25+P25</f>
-        <v>18.649999999999999</v>
-      </c>
-      <c r="R25" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="13">
-        <v>12</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="13">
-        <v>2</v>
-      </c>
-      <c r="E26" s="13">
-        <v>24</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="14">
-        <f>D26*2.2+E26*0.45</f>
-        <v>15.200000000000001</v>
-      </c>
-      <c r="M26" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F26)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F26)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F26)),-1,0), IF(ISNUMBER(SEARCH("后勤",F26)),1,0))</f>
-        <v>-1</v>
-      </c>
-      <c r="N26" s="14">
-        <v>2</v>
-      </c>
-      <c r="O26" s="14">
-        <f>N26*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14">
-        <f>L26+M26+O26+P26</f>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="R26" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="13">
-        <v>25</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="13">
-        <v>2</v>
-      </c>
-      <c r="E27" s="13">
-        <v>24</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="14">
-        <f>D27*2.2+E27*0.45</f>
-        <v>15.200000000000001</v>
-      </c>
-      <c r="M27" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F27)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F27)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F27)),-1,0), IF(ISNUMBER(SEARCH("后勤",F27)),1,0))</f>
-        <v>-1</v>
-      </c>
-      <c r="N27" s="14">
-        <v>2</v>
-      </c>
-      <c r="O27" s="14">
-        <f>N27*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14">
-        <f>L27+M27+O27+P27</f>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="R27" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A28" s="13">
-        <v>29</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="13">
-        <v>3</v>
-      </c>
-      <c r="E28" s="13">
-        <v>16</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="14">
-        <f>D28*2.2+E28*0.45</f>
-        <v>13.8</v>
-      </c>
-      <c r="M28" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F28)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F28)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F28)),-1,0), IF(ISNUMBER(SEARCH("后勤",F28)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N28" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="O28" s="14">
-        <f>N28*2.2</f>
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14">
-        <f>L28+M28+O28+P28</f>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="R28" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="13">
-        <v>32</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="13">
-        <v>2</v>
-      </c>
-      <c r="E29" s="13">
-        <v>24</v>
-      </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="14">
-        <f>D29*2.2+E29*0.45</f>
-        <v>15.200000000000001</v>
-      </c>
-      <c r="M29" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F29)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F29)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F29)),-1,0), IF(ISNUMBER(SEARCH("后勤",F29)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="O29" s="14">
-        <f>N29*2.2</f>
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14">
-        <f>L29+M29+O29+P29</f>
-        <v>18.5</v>
-      </c>
-      <c r="R29" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A30" s="13">
-        <v>21</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="13">
-        <v>3</v>
-      </c>
-      <c r="E30" s="13">
-        <v>19</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="14">
-        <f>D30*2.2+E30*0.45</f>
-        <v>15.150000000000002</v>
-      </c>
-      <c r="M30" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F30)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F30)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F30)),-1,0), IF(ISNUMBER(SEARCH("后勤",F30)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="O30" s="14">
-        <f>N30*2.2</f>
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14">
-        <f>L30+M30+O30+P30</f>
-        <v>18.450000000000003</v>
-      </c>
-      <c r="R30" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="13">
-        <v>4</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="13">
-        <v>4</v>
-      </c>
-      <c r="E31" s="13">
-        <v>18</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="25"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="14">
-        <f>D31*2.2+E31*0.45</f>
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M31" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F31)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F31)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F31)),-1,0), IF(ISNUMBER(SEARCH("后勤",F31)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N31" s="14">
-        <v>0</v>
-      </c>
-      <c r="O31" s="14">
-        <f>N31*2.2</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14">
-        <f>L31+M31+O31+P31</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="R31" s="14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="13">
-        <v>47</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="13">
-        <v>0</v>
-      </c>
-      <c r="E32" s="13">
-        <v>18</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="14">
-        <f>D32*2.2+E32*0.45</f>
-        <v>8.1</v>
-      </c>
-      <c r="M32" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F32)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F32)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F32)),-1,0), IF(ISNUMBER(SEARCH("后勤",F32)),1,0))</f>
-        <v>1.5</v>
-      </c>
-      <c r="N32" s="14">
-        <v>4</v>
-      </c>
-      <c r="O32" s="14">
-        <f>N32*2.2</f>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14">
-        <f>L32+M32+O32+P32</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="R32" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A33" s="13">
-        <v>3</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="13">
-        <v>1</v>
-      </c>
-      <c r="E33" s="13">
-        <v>21</v>
-      </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J33" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="K33" s="13"/>
-      <c r="L33" s="14">
-        <f>D33*2.2+E33*0.45</f>
-        <v>11.650000000000002</v>
-      </c>
-      <c r="M33" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F33)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F33)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F33)),-1,0), IF(ISNUMBER(SEARCH("后勤",F33)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="14">
-        <v>3</v>
-      </c>
-      <c r="O33" s="14">
-        <f>N33*2.2</f>
-        <v>6.6000000000000005</v>
-      </c>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14">
-        <f>L33+M33+O33+P33</f>
-        <v>18.250000000000004</v>
-      </c>
-      <c r="R33" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="13">
-        <v>13</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="13">
-        <v>2</v>
-      </c>
-      <c r="E34" s="13">
-        <v>33</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G34" s="25"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="14">
-        <f>D34*2.2+E34*0.45</f>
-        <v>19.25</v>
-      </c>
-      <c r="M34" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F34)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F34)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F34)),-1,0), IF(ISNUMBER(SEARCH("后勤",F34)),1,0))</f>
-        <v>-1</v>
-      </c>
-      <c r="N34" s="14">
-        <v>0</v>
-      </c>
-      <c r="O34" s="14">
-        <f>N34*2.2</f>
-        <v>0</v>
-      </c>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14">
-        <f>L34+M34+O34+P34</f>
-        <v>18.25</v>
-      </c>
-      <c r="R34" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A35" s="13">
-        <v>45</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="13">
-        <v>3</v>
-      </c>
-      <c r="E35" s="13">
-        <v>16</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="14">
-        <f>D35*2.2+E35*0.45</f>
-        <v>13.8</v>
-      </c>
-      <c r="M35" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F35)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F35)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F35)),-1,0), IF(ISNUMBER(SEARCH("后勤",F35)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="14">
-        <v>2</v>
-      </c>
-      <c r="O35" s="14">
-        <f>N35*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14">
-        <f>L35+M35+O35+P35</f>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10">
+        <f t="shared" si="7"/>
         <v>18.200000000000003</v>
       </c>
-      <c r="R35" s="14" t="s">
-        <v>168</v>
+      <c r="R35" s="10" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
@@ -4693,10 +4694,10 @@
         <v>49</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D36" s="4">
         <v>2</v>
@@ -4704,807 +4705,807 @@
       <c r="E36" s="4">
         <v>28</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G36" s="26" t="s">
-        <v>214</v>
+      <c r="G36" s="21" t="s">
+        <v>213</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="14">
-        <f>D36*2.2+E36*0.45</f>
+      <c r="L36" s="10">
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="M36" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F36)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F36)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F36)),-1,0), IF(ISNUMBER(SEARCH("后勤",F36)),1,0))</f>
+      <c r="M36" s="10">
+        <f t="shared" si="6"/>
         <v>-1</v>
       </c>
-      <c r="N36" s="14">
+      <c r="N36" s="10">
         <v>0</v>
       </c>
-      <c r="O36" s="14">
+      <c r="O36" s="10">
         <f>N36*0.45</f>
         <v>0</v>
       </c>
-      <c r="P36" s="14">
+      <c r="P36" s="10">
         <v>2</v>
       </c>
-      <c r="Q36" s="14">
-        <f>L36+M36+O36+P36</f>
+      <c r="Q36" s="10">
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="R36" s="14" t="s">
-        <v>178</v>
+      <c r="R36" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="A37" s="13">
+      <c r="A37" s="9">
         <v>31</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C37" s="13" t="s">
+      <c r="B37" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="9">
+        <v>3</v>
+      </c>
+      <c r="E37" s="9">
+        <v>18</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="13">
+      <c r="G37" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="10">
+        <f t="shared" si="5"/>
+        <v>14.7</v>
+      </c>
+      <c r="M37" s="10">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N37" s="10">
+        <v>1</v>
+      </c>
+      <c r="O37" s="10">
+        <f t="shared" ref="O37:O42" si="8">N37*2.2</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10">
+        <f t="shared" si="7"/>
+        <v>17.899999999999999</v>
+      </c>
+      <c r="R37" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>9</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="9">
+        <v>4</v>
+      </c>
+      <c r="E38" s="9">
+        <v>20</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="20"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="10">
+        <f t="shared" si="5"/>
+        <v>17.8</v>
+      </c>
+      <c r="M38" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10">
+        <f t="shared" si="7"/>
+        <v>17.8</v>
+      </c>
+      <c r="R38" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>37</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="9">
+        <v>2</v>
+      </c>
+      <c r="E39" s="9">
+        <v>20</v>
+      </c>
+      <c r="F39" s="9"/>
+      <c r="G39" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="10">
+        <f t="shared" si="5"/>
+        <v>13.4</v>
+      </c>
+      <c r="M39" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="10">
+        <v>2</v>
+      </c>
+      <c r="O39" s="10">
+        <f t="shared" si="8"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10">
+        <f t="shared" si="7"/>
+        <v>17.8</v>
+      </c>
+      <c r="R39" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A40" s="9">
+        <v>38</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="9">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9">
+        <v>27</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="10">
+        <f t="shared" si="5"/>
+        <v>12.15</v>
+      </c>
+      <c r="M40" s="10">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N40" s="10">
+        <v>2</v>
+      </c>
+      <c r="O40" s="10">
+        <f t="shared" si="8"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10">
+        <f t="shared" si="7"/>
+        <v>17.55</v>
+      </c>
+      <c r="R40" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A41" s="9">
+        <v>41</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="9">
+        <v>2</v>
+      </c>
+      <c r="E41" s="9">
+        <v>24</v>
+      </c>
+      <c r="F41" s="9"/>
+      <c r="G41" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="10">
+        <f t="shared" si="5"/>
+        <v>15.200000000000001</v>
+      </c>
+      <c r="M41" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="10">
+        <v>1</v>
+      </c>
+      <c r="O41" s="10">
+        <f t="shared" si="8"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10">
+        <f t="shared" si="7"/>
+        <v>17.400000000000002</v>
+      </c>
+      <c r="R41" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+      <c r="A42" s="9">
+        <v>5</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="9">
         <v>3</v>
       </c>
-      <c r="E37" s="13">
-        <v>18</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G37" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="14">
-        <f>D37*2.2+E37*0.45</f>
-        <v>14.7</v>
-      </c>
-      <c r="M37" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F37)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F37)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F37)),-1,0), IF(ISNUMBER(SEARCH("后勤",F37)),1,0))</f>
+      <c r="E42" s="9">
+        <v>19</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="10">
+        <f t="shared" si="5"/>
+        <v>15.150000000000002</v>
+      </c>
+      <c r="M42" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="10">
         <v>1</v>
       </c>
-      <c r="N37" s="14">
-        <v>1</v>
-      </c>
-      <c r="O37" s="14">
-        <f>N37*2.2</f>
+      <c r="O42" s="10">
+        <f t="shared" si="8"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14">
-        <f>L37+M37+O37+P37</f>
-        <v>17.899999999999999</v>
-      </c>
-      <c r="R37" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="13">
-        <v>9</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="13">
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10">
+        <f t="shared" si="7"/>
+        <v>17.350000000000001</v>
+      </c>
+      <c r="R42" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+      <c r="A43" s="9">
+        <v>14</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="9">
         <v>4</v>
       </c>
-      <c r="E38" s="13">
-        <v>20</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="25"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="14">
-        <f>D38*2.2+E38*0.45</f>
-        <v>17.8</v>
-      </c>
-      <c r="M38" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F38)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F38)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F38)),-1,0), IF(ISNUMBER(SEARCH("后勤",F38)),1,0))</f>
+      <c r="E43" s="9">
+        <v>15</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="10">
+        <f t="shared" si="5"/>
+        <v>15.55</v>
+      </c>
+      <c r="M43" s="10">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14">
-        <f>N38*2.2</f>
-        <v>0</v>
-      </c>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="14">
-        <f>L38+M38+O38+P38</f>
-        <v>17.8</v>
-      </c>
-      <c r="R38" s="14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="13">
-        <v>37</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="13">
-        <v>2</v>
-      </c>
-      <c r="E39" s="13">
-        <v>20</v>
-      </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="14">
-        <f>D39*2.2+E39*0.45</f>
-        <v>13.4</v>
-      </c>
-      <c r="M39" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F39)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F39)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F39)),-1,0), IF(ISNUMBER(SEARCH("后勤",F39)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N39" s="14">
-        <v>2</v>
-      </c>
-      <c r="O39" s="14">
-        <f>N39*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="14">
-        <f>L39+M39+O39+P39</f>
-        <v>17.8</v>
-      </c>
-      <c r="R39" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A40" s="13">
-        <v>38</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" s="13">
-        <v>0</v>
-      </c>
-      <c r="E40" s="13">
-        <v>27</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G40" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="14">
-        <f>D40*2.2+E40*0.45</f>
-        <v>12.15</v>
-      </c>
-      <c r="M40" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F40)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F40)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F40)),-1,0), IF(ISNUMBER(SEARCH("后勤",F40)),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="N40" s="14">
-        <v>2</v>
-      </c>
-      <c r="O40" s="14">
-        <f>N40*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="14">
-        <f>L40+M40+O40+P40</f>
-        <v>17.55</v>
-      </c>
-      <c r="R40" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
-      <c r="A41" s="13">
-        <v>41</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D41" s="13">
-        <v>2</v>
-      </c>
-      <c r="E41" s="13">
-        <v>24</v>
-      </c>
-      <c r="F41" s="13"/>
-      <c r="G41" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="14">
-        <f>D41*2.2+E41*0.45</f>
-        <v>15.200000000000001</v>
-      </c>
-      <c r="M41" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F41)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F41)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F41)),-1,0), IF(ISNUMBER(SEARCH("后勤",F41)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N41" s="14">
-        <v>1</v>
-      </c>
-      <c r="O41" s="14">
-        <f>N41*2.2</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14">
-        <f>L41+M41+O41+P41</f>
-        <v>17.400000000000002</v>
-      </c>
-      <c r="R41" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A42" s="13">
-        <v>5</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" s="13">
-        <v>3</v>
-      </c>
-      <c r="E42" s="13">
-        <v>19</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="14">
-        <f>D42*2.2+E42*0.45</f>
-        <v>15.150000000000002</v>
-      </c>
-      <c r="M42" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F42)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F42)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F42)),-1,0), IF(ISNUMBER(SEARCH("后勤",F42)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N42" s="14">
-        <v>1</v>
-      </c>
-      <c r="O42" s="14">
-        <f>N42*2.2</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P42" s="14"/>
-      <c r="Q42" s="14">
-        <f>L42+M42+O42+P42</f>
-        <v>17.350000000000001</v>
-      </c>
-      <c r="R42" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A43" s="13">
-        <v>14</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" s="13">
+      <c r="N43" s="10">
         <v>4</v>
       </c>
-      <c r="E43" s="13">
-        <v>15</v>
-      </c>
-      <c r="F43" s="13"/>
-      <c r="G43" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="14">
-        <f>D43*2.2+E43*0.45</f>
-        <v>15.55</v>
-      </c>
-      <c r="M43" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F43)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F43)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F43)),-1,0), IF(ISNUMBER(SEARCH("后勤",F43)),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="N43" s="14">
-        <v>4</v>
-      </c>
-      <c r="O43" s="14">
+      <c r="O43" s="10">
         <f>N43*0.45</f>
         <v>1.8</v>
       </c>
-      <c r="P43" s="14"/>
-      <c r="Q43" s="14">
-        <f>L43+M43+O43+P43</f>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10">
+        <f t="shared" si="7"/>
         <v>17.350000000000001</v>
       </c>
-      <c r="R43" s="14" t="s">
-        <v>177</v>
+      <c r="R43" s="10" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A44" s="13">
+      <c r="A44" s="9">
         <v>24</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="13">
+      <c r="B44" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="9">
         <v>2</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="9">
         <v>21</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G44" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="14">
-        <f>D44*2.2+E44*0.45</f>
+      <c r="G44" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="10">
+        <f t="shared" si="5"/>
         <v>13.850000000000001</v>
       </c>
-      <c r="M44" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F44)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F44)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F44)),-1,0), IF(ISNUMBER(SEARCH("后勤",F44)),1,0))</f>
+      <c r="M44" s="10">
+        <f t="shared" si="6"/>
         <v>-1</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="10">
         <v>2</v>
       </c>
-      <c r="O44" s="14">
+      <c r="O44" s="10">
         <f>N44*2.2</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="P44" s="14"/>
-      <c r="Q44" s="14">
-        <f>L44+M44+O44+P44</f>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10">
+        <f t="shared" si="7"/>
         <v>17.25</v>
       </c>
-      <c r="R44" s="14" t="s">
-        <v>178</v>
+      <c r="R44" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="13">
+      <c r="A45" s="9">
         <v>43</v>
       </c>
-      <c r="B45" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D45" s="13">
+      <c r="B45" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="9">
         <v>1</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="9">
         <v>14</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G45" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="14">
-        <f>D45*2.2+E45*0.45</f>
+      <c r="G45" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="10">
+        <f t="shared" si="5"/>
         <v>8.5</v>
       </c>
-      <c r="M45" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F45)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F45)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F45)),-1,0), IF(ISNUMBER(SEARCH("后勤",F45)),1,0))</f>
+      <c r="M45" s="10">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="10">
         <v>6</v>
       </c>
-      <c r="O45" s="14">
+      <c r="O45" s="10">
         <f>N45*0.45</f>
         <v>2.7</v>
       </c>
-      <c r="P45" s="14">
+      <c r="P45" s="10">
         <v>6</v>
       </c>
-      <c r="Q45" s="14">
-        <f>L45+M45+O45+P45</f>
+      <c r="Q45" s="10">
+        <f t="shared" si="7"/>
         <v>17.2</v>
       </c>
-      <c r="R45" s="14" t="s">
+      <c r="R45" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A46" s="9">
+        <v>19</v>
+      </c>
+      <c r="B46" s="10" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A46" s="13">
-        <v>19</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46" s="9">
         <v>1</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="9">
         <v>18</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G46" s="25" t="s">
+      <c r="G46" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="H46" s="13" t="s">
+      <c r="H46" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
-      <c r="L46" s="14">
-        <f>D46*2.2+E46*0.45</f>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="10">
+        <f t="shared" si="5"/>
         <v>10.3</v>
       </c>
-      <c r="M46" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F46)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F46)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F46)),-1,0), IF(ISNUMBER(SEARCH("后勤",F46)),1,0))</f>
+      <c r="M46" s="10">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N46" s="14">
+      <c r="N46" s="10">
         <v>3</v>
       </c>
-      <c r="O46" s="14">
+      <c r="O46" s="10">
         <f>N46*2.2</f>
         <v>6.6000000000000005</v>
       </c>
-      <c r="P46" s="14"/>
-      <c r="Q46" s="14">
-        <f>L46+M46+O46+P46</f>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10">
+        <f t="shared" si="7"/>
         <v>16.900000000000002</v>
       </c>
-      <c r="R46" s="14" t="s">
+      <c r="R46" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+      <c r="A47" s="9">
+        <v>6</v>
+      </c>
+      <c r="B47" s="10" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" ht="45" x14ac:dyDescent="0.2">
-      <c r="A47" s="13">
-        <v>6</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47" s="9">
         <v>3</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="9">
         <v>16</v>
       </c>
-      <c r="F47" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G47" s="25" t="s">
+      <c r="F47" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G47" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H47" s="13" t="s">
+      <c r="H47" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
-      <c r="L47" s="14">
-        <f>D47*2.2+E47*0.45</f>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="10">
+        <f t="shared" si="5"/>
         <v>13.8</v>
       </c>
-      <c r="M47" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F47)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F47)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F47)),-1,0), IF(ISNUMBER(SEARCH("后勤",F47)),1,0))</f>
+      <c r="M47" s="10">
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
-      <c r="N47" s="14">
+      <c r="N47" s="10">
         <v>3</v>
       </c>
-      <c r="O47" s="14">
+      <c r="O47" s="10">
         <f>N47*0.45</f>
         <v>1.35</v>
       </c>
-      <c r="P47" s="14"/>
-      <c r="Q47" s="14">
-        <f>L47+M47+O47+P47</f>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10">
+        <f t="shared" si="7"/>
         <v>16.650000000000002</v>
       </c>
-      <c r="R47" s="14" t="s">
-        <v>169</v>
+      <c r="R47" s="10" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="13">
+      <c r="A48" s="9">
         <v>36</v>
       </c>
-      <c r="B48" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C48" s="13" t="s">
+      <c r="B48" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="9">
+        <v>2</v>
+      </c>
+      <c r="E48" s="9">
+        <v>20</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G48" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="D48" s="13">
-        <v>2</v>
-      </c>
-      <c r="E48" s="13">
-        <v>20</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="G48" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="14">
-        <f>D48*2.2+E48*0.45</f>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="10">
+        <f t="shared" si="5"/>
         <v>13.4</v>
       </c>
-      <c r="M48" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F48)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F48)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F48)),-1,0), IF(ISNUMBER(SEARCH("后勤",F48)),1,0))</f>
+      <c r="M48" s="10">
+        <f t="shared" si="6"/>
         <v>-1</v>
       </c>
-      <c r="N48" s="14">
+      <c r="N48" s="10">
         <v>8</v>
       </c>
-      <c r="O48" s="14">
+      <c r="O48" s="10">
         <f>N48*0.45</f>
         <v>3.6</v>
       </c>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14">
-        <f>L48+M48+O48+P48</f>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10">
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
-      <c r="R48" s="14" t="s">
-        <v>178</v>
+      <c r="R48" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A49" s="13">
+      <c r="A49" s="9">
         <v>33</v>
       </c>
-      <c r="B49" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C49" s="13" t="s">
+      <c r="B49" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="9">
         <v>1</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="9">
         <v>18</v>
       </c>
-      <c r="F49" s="13" t="s">
+      <c r="F49" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G49" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="14">
-        <f>D49*2.2+E49*0.45</f>
+      <c r="G49" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="10">
+        <f t="shared" si="5"/>
         <v>10.3</v>
       </c>
-      <c r="M49" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F49)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F49)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F49)),-1,0), IF(ISNUMBER(SEARCH("后勤",F49)),1,0))</f>
+      <c r="M49" s="10">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N49" s="14">
+      <c r="N49" s="10">
         <v>2.5</v>
       </c>
-      <c r="O49" s="14">
+      <c r="O49" s="10">
         <f>N49*2.2</f>
         <v>5.5</v>
       </c>
-      <c r="P49" s="14"/>
-      <c r="Q49" s="14">
-        <f>L49+M49+O49+P49</f>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10">
+        <f t="shared" si="7"/>
         <v>15.8</v>
       </c>
-      <c r="R49" s="14" t="s">
-        <v>177</v>
+      <c r="R49" s="10" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="34">
+      <c r="A50" s="27">
         <v>8</v>
       </c>
-      <c r="B50" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C50" s="34" t="s">
+      <c r="B50" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="27">
         <v>2</v>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="27">
         <v>20</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="H50" s="34" t="s">
+      <c r="G50" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H50" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="14">
-        <f>D50*2.2+E50*0.45</f>
+      <c r="I50" s="27"/>
+      <c r="J50" s="27"/>
+      <c r="K50" s="27"/>
+      <c r="L50" s="10">
+        <f t="shared" si="5"/>
         <v>13.4</v>
       </c>
-      <c r="M50" s="14">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F50)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F50)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F50)),-1,0), IF(ISNUMBER(SEARCH("后勤",F50)),1,0))</f>
+      <c r="M50" s="10">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N50" s="14">
+      <c r="N50" s="10">
         <v>4</v>
       </c>
-      <c r="O50" s="14">
+      <c r="O50" s="10">
         <f>N50*0.45</f>
         <v>1.8</v>
       </c>
-      <c r="P50" s="14"/>
-      <c r="Q50" s="14">
-        <f>L50+M50+O50+P50</f>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10">
+        <f t="shared" si="7"/>
         <v>15.200000000000001</v>
       </c>
-      <c r="R50" s="14" t="s">
-        <v>169</v>
+      <c r="R50" s="10" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="14"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
     </row>
     <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="C52" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="D52" s="9">
+        <v>1</v>
+      </c>
+      <c r="E52" s="9">
+        <v>1</v>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="D52" s="13">
-        <v>1</v>
-      </c>
-      <c r="E52" s="13">
-        <v>1</v>
-      </c>
-      <c r="F52" s="13"/>
-      <c r="G52" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="14">
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="10">
         <f>D52*2.2+E52*0.45</f>
         <v>2.6500000000000004</v>
       </c>
-      <c r="M52" s="14">
+      <c r="M52" s="10">
         <f>SUM(IF(ISNUMBER(SEARCH("疾行",F52)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F52)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F52)),-1,0), IF(ISNUMBER(SEARCH("后勤",F52)),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="14"/>
-      <c r="Q52" s="14"/>
-      <c r="R52" s="14"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R53" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -5522,38 +5523,38 @@
   <dimension ref="A4:Q26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="4" spans="1:17" s="11" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+    </row>
+    <row r="6" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-    </row>
-    <row r="6" spans="1:17" s="11" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -5571,150 +5572,150 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:17" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+    </row>
+    <row r="8" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-    </row>
-    <row r="8" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="24" t="s">
+      <c r="B8" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+    </row>
+    <row r="9" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-    </row>
-    <row r="9" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+    </row>
+    <row r="10" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-    </row>
-    <row r="10" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24" t="s">
+      <c r="B10" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+    </row>
+    <row r="11" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B11" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-    </row>
-    <row r="11" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="24" t="s">
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B12" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-    </row>
-    <row r="12" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-    </row>
-    <row r="13" spans="1:17" s="11" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:17" s="11" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+    </row>
+    <row r="13" spans="1:17" s="7" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+    </row>
+    <row r="15" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:17" s="11" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="B15" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -5732,245 +5733,245 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+    </row>
+    <row r="17" spans="1:17" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B17" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+    </row>
+    <row r="18" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-    </row>
-    <row r="17" spans="1:17" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-    </row>
-    <row r="18" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B19" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-    </row>
-    <row r="19" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+    </row>
+    <row r="20" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B20" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-    </row>
-    <row r="20" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B21" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+    </row>
+    <row r="22" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-    </row>
-    <row r="21" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-    </row>
-    <row r="22" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+    </row>
+    <row r="23" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B23" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+    </row>
+    <row r="24" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-    </row>
-    <row r="23" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-    </row>
-    <row r="24" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B24" s="32" t="s">
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+    </row>
+    <row r="25" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B25" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-    </row>
-    <row r="25" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-    </row>
-    <row r="26" spans="1:17" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+    </row>
+    <row r="26" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5990,22 +5991,22 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="B5" s="31"/>
+      <c r="A5" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="33"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
-        <v>173</v>
+      <c r="A7" s="10" t="s">
+        <v>172</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A7)</f>
@@ -6013,8 +6014,8 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
-        <v>170</v>
+      <c r="A8" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="B8" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A8)</f>
@@ -6022,8 +6023,8 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
-        <v>172</v>
+      <c r="A9" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="B9" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A9)</f>
@@ -6031,8 +6032,8 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
-        <v>174</v>
+      <c r="A10" s="10" t="s">
+        <v>173</v>
       </c>
       <c r="B10" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A10)</f>
@@ -6040,8 +6041,8 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
-        <v>175</v>
+      <c r="A11" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="B11" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A11)</f>
@@ -6052,16 +6053,16 @@
       <c r="B12" s="2"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>198</v>
       </c>
       <c r="B14" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A14)</f>
@@ -6069,8 +6070,8 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
-        <v>199</v>
+      <c r="A15" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="B15" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A15)</f>
@@ -6078,8 +6079,8 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
-        <v>200</v>
+      <c r="A16" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A16)</f>
@@ -6087,8 +6088,8 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
-        <v>166</v>
+      <c r="A17" s="10" t="s">
+        <v>165</v>
       </c>
       <c r="B17" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A17)</f>
@@ -6114,47 +6115,47 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+        <v>111</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12">
         <v>18.75</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="G12" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" t="s">
         <v>113</v>
       </c>
-      <c r="D13" t="s">
-        <v>114</v>
-      </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" t="s">
         <v>121</v>
-      </c>
-      <c r="H13" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -6170,7 +6171,7 @@
         <v>18.75</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -6189,7 +6190,7 @@
         <v>18.75</v>
       </c>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -6208,7 +6209,7 @@
         <v>18.75</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -6227,7 +6228,7 @@
         <v>18.75</v>
       </c>
       <c r="G17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -6246,7 +6247,7 @@
         <v>18.75</v>
       </c>
       <c r="G18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H18">
         <v>1</v>

--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14845537-D945-4562-B8C4-AE413542DE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133BC257-F37F-43A1-81CA-DE83E3001BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色列表" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="222">
   <si>
     <t>No.</t>
   </si>
@@ -180,9 +180,6 @@
     <t>烛火</t>
   </si>
   <si>
-    <t>&lt;疾行&gt;&lt;后勤&gt;</t>
-  </si>
-  <si>
     <t>移动后，伤害所有相邻的敌人。</t>
   </si>
   <si>
@@ -244,9 +241,6 @@
   </si>
   <si>
     <t>暗域</t>
-  </si>
-  <si>
-    <t>&lt;疾行&gt; &lt;渗透&gt;</t>
   </si>
   <si>
     <t>攻击时，和对象交换位置。</t>
@@ -2190,7 +2184,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>每当敌人受到一次伤害，你的攻击力</t>
+      <t>我方回合内，每当敌人受到一次伤害，你的攻击力</t>
     </r>
     <r>
       <rPr>
@@ -2209,7 +2203,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>，直至回合结束。</t>
+      <t>，对方回合结束时消失。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2270,6 +2264,132 @@
   </si>
   <si>
     <t>敌方回合，一名己方英雄受到伤害后，其获得[圣盾]，一回合限一次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疾行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&gt;
+&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>渗透</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疾行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&gt;
+&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后勤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AOE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和多段</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能提供攻击力加成的角色</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2509,7 +2629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2588,6 +2708,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2910,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>1</v>
@@ -2940,36 +3063,36 @@
         <v>9</v>
       </c>
       <c r="L1" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="P1" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q1" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>127</v>
-      </c>
       <c r="R1" s="14" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>27</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" s="9">
         <v>3</v>
@@ -2978,15 +3101,15 @@
         <v>20</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" s="9"/>
+        <v>59</v>
+      </c>
+      <c r="I2" s="11"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="10">
@@ -3010,7 +3133,7 @@
         <v>21.900000000000002</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="57" x14ac:dyDescent="0.2">
@@ -3018,10 +3141,10 @@
         <v>34</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D3" s="9">
         <v>3</v>
@@ -3030,16 +3153,16 @@
         <v>15</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
@@ -3064,7 +3187,7 @@
         <v>21.450000000000003</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3072,10 +3195,10 @@
         <v>40</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D4" s="9">
         <v>5</v>
@@ -3085,9 +3208,9 @@
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="H4" s="9"/>
+        <v>184</v>
+      </c>
+      <c r="H4" s="11"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
@@ -3112,15 +3235,15 @@
         <v>21.25</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>17</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>48</v>
@@ -3132,13 +3255,13 @@
         <v>17</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>29</v>
+      <c r="H5" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -3164,7 +3287,7 @@
         <v>21.15</v>
       </c>
       <c r="R5" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -3172,22 +3295,22 @@
         <v>22</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" s="9">
         <v>2</v>
       </c>
       <c r="E6" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -3195,7 +3318,7 @@
       <c r="K6" s="9"/>
       <c r="L6" s="10">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>13.850000000000001</v>
       </c>
       <c r="M6" s="10">
         <f t="shared" si="1"/>
@@ -3209,14 +3332,14 @@
         <v>1.35</v>
       </c>
       <c r="P6" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="10">
         <f t="shared" si="2"/>
-        <v>20.85</v>
+        <v>18.200000000000003</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -3224,10 +3347,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="9">
         <v>3</v>
@@ -3239,7 +3362,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>29</v>
@@ -3268,7 +3391,7 @@
         <v>20.6</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -3276,10 +3399,10 @@
         <v>42</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D8" s="9">
         <v>2</v>
@@ -3291,7 +3414,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -3318,7 +3441,7 @@
         <v>20.6</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="69" x14ac:dyDescent="0.2">
@@ -3326,10 +3449,10 @@
         <v>30</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D9" s="9">
         <v>3</v>
@@ -3339,10 +3462,10 @@
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -3368,7 +3491,7 @@
         <v>20</v>
       </c>
       <c r="R9" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -3376,10 +3499,10 @@
         <v>35</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
@@ -3391,10 +3514,10 @@
         <v>21</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -3420,7 +3543,7 @@
         <v>20</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3428,10 +3551,10 @@
         <v>20</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="9">
         <v>3</v>
@@ -3440,16 +3563,16 @@
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
@@ -3474,7 +3597,7 @@
         <v>19.550000000000004</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -3482,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>43</v>
@@ -3526,7 +3649,7 @@
         <v>19.5</v>
       </c>
       <c r="R12" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -3534,10 +3657,10 @@
         <v>23</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="9">
         <v>2</v>
@@ -3549,7 +3672,7 @@
         <v>34</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -3576,7 +3699,7 @@
         <v>19.5</v>
       </c>
       <c r="R13" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -3584,10 +3707,10 @@
         <v>44</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D14" s="9">
         <v>2</v>
@@ -3599,11 +3722,11 @@
         <v>34</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
@@ -3628,7 +3751,7 @@
         <v>19.5</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -3636,7 +3759,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>33</v>
@@ -3678,7 +3801,7 @@
         <v>19.2</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -3686,10 +3809,10 @@
         <v>28</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D16" s="9">
         <v>3</v>
@@ -3699,10 +3822,10 @@
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
@@ -3728,7 +3851,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R16" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -3736,7 +3859,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>13</v>
@@ -3780,7 +3903,7 @@
         <v>18.900000000000002</v>
       </c>
       <c r="R17" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3788,7 +3911,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>31</v>
@@ -3800,7 +3923,7 @@
         <v>19</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>32</v>
@@ -3832,7 +3955,7 @@
         <v>18.850000000000001</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -3840,10 +3963,10 @@
         <v>46</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D19" s="9">
         <v>2</v>
@@ -3852,14 +3975,14 @@
         <v>19</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
@@ -3884,7 +4007,7 @@
         <v>18.850000000000001</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3892,7 +4015,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>26</v>
@@ -3904,7 +4027,7 @@
         <v>14</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G20" s="20"/>
       <c r="H20" s="9" t="s">
@@ -3932,7 +4055,7 @@
         <v>18.8</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3940,10 +4063,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" s="9">
         <v>2</v>
@@ -3952,10 +4075,10 @@
         <v>26</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -3982,7 +4105,7 @@
         <v>18.8</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -3990,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>10</v>
@@ -4032,7 +4155,7 @@
         <v>18.75</v>
       </c>
       <c r="R22" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
@@ -4040,10 +4163,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D23" s="9">
         <v>1</v>
@@ -4055,7 +4178,7 @@
         <v>34</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="9"/>
@@ -4082,7 +4205,7 @@
         <v>18.75</v>
       </c>
       <c r="R23" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4090,7 +4213,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>45</v>
@@ -4132,7 +4255,7 @@
         <v>18.7</v>
       </c>
       <c r="R24" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -4140,10 +4263,10 @@
         <v>39</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D25" s="9">
         <v>3</v>
@@ -4155,7 +4278,7 @@
         <v>46</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -4182,7 +4305,7 @@
         <v>18.649999999999999</v>
       </c>
       <c r="R25" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4190,7 +4313,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>36</v>
@@ -4232,7 +4355,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R26" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -4240,10 +4363,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" s="9">
         <v>2</v>
@@ -4255,11 +4378,11 @@
         <v>34</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
@@ -4284,7 +4407,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R27" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -4292,10 +4415,10 @@
         <v>29</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D28" s="9">
         <v>3</v>
@@ -4304,10 +4427,10 @@
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -4334,7 +4457,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R28" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -4342,10 +4465,10 @@
         <v>32</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D29" s="9">
         <v>2</v>
@@ -4355,7 +4478,7 @@
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>29</v>
@@ -4384,7 +4507,7 @@
         <v>18.5</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -4392,10 +4515,10 @@
         <v>21</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" s="9">
         <v>3</v>
@@ -4407,10 +4530,10 @@
         <v>21</v>
       </c>
       <c r="G30" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>60</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
@@ -4436,7 +4559,7 @@
         <v>18.450000000000003</v>
       </c>
       <c r="R30" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4444,7 +4567,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>19</v>
@@ -4484,7 +4607,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="R31" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -4492,10 +4615,10 @@
         <v>47</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D32" s="9">
         <v>0</v>
@@ -4507,10 +4630,10 @@
         <v>14</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
@@ -4536,7 +4659,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="R32" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -4544,7 +4667,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>17</v>
@@ -4561,10 +4684,10 @@
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="10">
@@ -4588,7 +4711,7 @@
         <v>18.250000000000004</v>
       </c>
       <c r="R33" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4596,7 +4719,7 @@
         <v>13</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>39</v>
@@ -4636,7 +4759,7 @@
         <v>18.25</v>
       </c>
       <c r="R34" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="60" x14ac:dyDescent="0.2">
@@ -4644,10 +4767,10 @@
         <v>45</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D35" s="9">
         <v>3</v>
@@ -4659,7 +4782,7 @@
         <v>21</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -4686,7 +4809,7 @@
         <v>18.200000000000003</v>
       </c>
       <c r="R35" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
@@ -4694,22 +4817,22 @@
         <v>49</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D36" s="4">
         <v>2</v>
       </c>
       <c r="E36" s="4">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -4717,7 +4840,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="10">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>14.3</v>
       </c>
       <c r="M36" s="10">
         <f t="shared" si="6"/>
@@ -4735,10 +4858,10 @@
       </c>
       <c r="Q36" s="10">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>15.3</v>
       </c>
       <c r="R36" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
@@ -4746,10 +4869,10 @@
         <v>31</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D37" s="9">
         <v>3</v>
@@ -4758,10 +4881,10 @@
         <v>18</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -4788,7 +4911,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="R37" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4796,7 +4919,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>30</v>
@@ -4834,18 +4957,18 @@
         <v>17.8</v>
       </c>
       <c r="R38" s="10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D39" s="9">
         <v>2</v>
@@ -4855,10 +4978,10 @@
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>38</v>
+        <v>214</v>
+      </c>
+      <c r="H39" s="28" t="s">
+        <v>220</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
@@ -4884,7 +5007,7 @@
         <v>17.8</v>
       </c>
       <c r="R39" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -4892,10 +5015,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D40" s="9">
         <v>0</v>
@@ -4904,10 +5027,10 @@
         <v>27</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
@@ -4934,7 +5057,7 @@
         <v>17.55</v>
       </c>
       <c r="R40" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -4942,10 +5065,10 @@
         <v>41</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D41" s="9">
         <v>2</v>
@@ -4955,10 +5078,10 @@
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
@@ -4984,7 +5107,7 @@
         <v>17.400000000000002</v>
       </c>
       <c r="R41" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -4992,7 +5115,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>20</v>
@@ -5007,7 +5130,7 @@
         <v>21</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>22</v>
@@ -5036,7 +5159,7 @@
         <v>17.350000000000001</v>
       </c>
       <c r="R42" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -5044,7 +5167,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>40</v>
@@ -5086,7 +5209,7 @@
         <v>17.350000000000001</v>
       </c>
       <c r="R43" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -5094,10 +5217,10 @@
         <v>24</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D44" s="9">
         <v>2</v>
@@ -5109,7 +5232,7 @@
         <v>34</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -5136,7 +5259,7 @@
         <v>17.25</v>
       </c>
       <c r="R44" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -5144,10 +5267,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D45" s="9">
         <v>1</v>
@@ -5159,7 +5282,7 @@
         <v>21</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -5188,7 +5311,7 @@
         <v>17.2</v>
       </c>
       <c r="R45" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -5196,10 +5319,10 @@
         <v>19</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" s="9">
         <v>1</v>
@@ -5211,10 +5334,10 @@
         <v>21</v>
       </c>
       <c r="G46" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="9"/>
@@ -5240,7 +5363,7 @@
         <v>16.900000000000002</v>
       </c>
       <c r="R46" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -5248,7 +5371,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>23</v>
@@ -5260,7 +5383,7 @@
         <v>16</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G47" s="20" t="s">
         <v>24</v>
@@ -5292,7 +5415,7 @@
         <v>16.650000000000002</v>
       </c>
       <c r="R47" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -5300,10 +5423,10 @@
         <v>36</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D48" s="9">
         <v>2</v>
@@ -5312,10 +5435,10 @@
         <v>20</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
@@ -5342,7 +5465,7 @@
         <v>16</v>
       </c>
       <c r="R48" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -5350,7 +5473,7 @@
         <v>33</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>38</v>
@@ -5365,10 +5488,10 @@
         <v>21</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
@@ -5394,7 +5517,7 @@
         <v>15.8</v>
       </c>
       <c r="R49" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -5402,7 +5525,7 @@
         <v>8</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C50" s="27" t="s">
         <v>28</v>
@@ -5417,7 +5540,7 @@
         <v>21</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H50" s="27" t="s">
         <v>29</v>
@@ -5446,7 +5569,7 @@
         <v>15.200000000000001</v>
       </c>
       <c r="R50" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -5471,13 +5594,13 @@
     </row>
     <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="D52" s="9">
         <v>1</v>
@@ -5487,7 +5610,7 @@
       </c>
       <c r="F52" s="9"/>
       <c r="G52" s="20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
@@ -5524,37 +5647,37 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
+      <c r="A4" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
+      <c r="A5" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -5574,10 +5697,10 @@
     </row>
     <row r="7" spans="1:17" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -5586,10 +5709,10 @@
     </row>
     <row r="8" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -5609,10 +5732,10 @@
     </row>
     <row r="9" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -5632,10 +5755,10 @@
     </row>
     <row r="10" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -5655,10 +5778,10 @@
     </row>
     <row r="11" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -5678,10 +5801,10 @@
     </row>
     <row r="12" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -5701,21 +5824,21 @@
     </row>
     <row r="13" spans="1:17" s="7" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="A14" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
     </row>
     <row r="15" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -5735,10 +5858,10 @@
     </row>
     <row r="16" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -5758,10 +5881,10 @@
     </row>
     <row r="17" spans="1:17" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -5781,10 +5904,10 @@
     </row>
     <row r="18" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -5804,10 +5927,10 @@
     </row>
     <row r="19" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -5827,10 +5950,10 @@
     </row>
     <row r="20" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -5850,10 +5973,10 @@
     </row>
     <row r="21" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -5873,10 +5996,10 @@
     </row>
     <row r="22" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -5896,10 +6019,10 @@
     </row>
     <row r="23" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -5919,10 +6042,10 @@
     </row>
     <row r="24" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -5942,10 +6065,10 @@
     </row>
     <row r="25" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -5964,14 +6087,14 @@
       <c r="Q25" s="17"/>
     </row>
     <row r="26" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
+      <c r="A26" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5991,22 +6114,22 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="B5" s="33"/>
+      <c r="A5" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="34"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A7)</f>
@@ -6015,7 +6138,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B8" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A8)</f>
@@ -6024,7 +6147,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B9" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A9)</f>
@@ -6033,7 +6156,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A10)</f>
@@ -6042,7 +6165,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B11" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A11)</f>
@@ -6054,15 +6177,15 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B14" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A14)</f>
@@ -6071,7 +6194,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B15" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A15)</f>
@@ -6080,7 +6203,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B16" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A16)</f>
@@ -6089,7 +6212,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B17" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A17)</f>
@@ -6115,47 +6238,47 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
+        <v>109</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E12">
         <v>18.75</v>
       </c>
-      <c r="G12" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="H12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
+      <c r="G12" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -6171,7 +6294,7 @@
         <v>18.75</v>
       </c>
       <c r="G14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -6190,7 +6313,7 @@
         <v>18.75</v>
       </c>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -6209,7 +6332,7 @@
         <v>18.75</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -6228,7 +6351,7 @@
         <v>18.75</v>
       </c>
       <c r="G17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -6247,7 +6370,7 @@
         <v>18.75</v>
       </c>
       <c r="G18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H18">
         <v>1</v>

--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133BC257-F37F-43A1-81CA-DE83E3001BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6A9321-B712-4D13-B3F8-7748A5757F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1755" yWindow="4800" windowWidth="28800" windowHeight="15645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色列表" sheetId="1" r:id="rId1"/>
@@ -1139,10 +1139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对方回合结束时，随机变为己方队伍中的一名其他角色，暂时获得其所有技能和特性，直到下次变化为止。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>白板</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2390,6 +2386,10 @@
   </si>
   <si>
     <t>能提供攻击力加成的角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我方回合开始时，随机变为己方队伍中的一名其他角色，暂时获得其所有技能和特性，直到下次变化为止。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>1</v>
@@ -3081,7 +3081,7 @@
         <v>125</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>69</v>
@@ -3101,7 +3101,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>70</v>
@@ -3133,7 +3133,7 @@
         <v>21.900000000000002</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="57" x14ac:dyDescent="0.2">
@@ -3141,7 +3141,7 @@
         <v>34</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>81</v>
@@ -3187,7 +3187,7 @@
         <v>21.450000000000003</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3195,7 +3195,7 @@
         <v>40</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>90</v>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="9"/>
@@ -3235,7 +3235,7 @@
         <v>21.25</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3243,7 +3243,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>48</v>
@@ -3255,13 +3255,13 @@
         <v>17</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>49</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -3287,7 +3287,7 @@
         <v>21.15</v>
       </c>
       <c r="R5" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -3295,7 +3295,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>60</v>
@@ -3310,7 +3310,7 @@
         <v>34</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -3339,7 +3339,7 @@
         <v>18.200000000000003</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -3347,7 +3347,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>50</v>
@@ -3391,7 +3391,7 @@
         <v>20.6</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -3399,7 +3399,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>92</v>
@@ -3414,7 +3414,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -3441,7 +3441,7 @@
         <v>20.6</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="69" x14ac:dyDescent="0.2">
@@ -3449,7 +3449,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>71</v>
@@ -3491,7 +3491,7 @@
         <v>20</v>
       </c>
       <c r="R9" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -3499,10 +3499,10 @@
         <v>35</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>172</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>173</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
@@ -3514,7 +3514,7 @@
         <v>21</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>131</v>
@@ -3543,7 +3543,7 @@
         <v>20</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3551,7 +3551,7 @@
         <v>20</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>55</v>
@@ -3563,10 +3563,10 @@
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>29</v>
@@ -3597,7 +3597,7 @@
         <v>19.550000000000004</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -3605,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>43</v>
@@ -3649,7 +3649,7 @@
         <v>19.5</v>
       </c>
       <c r="R12" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -3657,7 +3657,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>61</v>
@@ -3699,7 +3699,7 @@
         <v>19.5</v>
       </c>
       <c r="R13" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -3707,7 +3707,7 @@
         <v>44</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>94</v>
@@ -3751,7 +3751,7 @@
         <v>19.5</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -3759,7 +3759,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>33</v>
@@ -3801,7 +3801,7 @@
         <v>19.2</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -3809,7 +3809,7 @@
         <v>28</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>72</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="22" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>128</v>
@@ -3851,7 +3851,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R16" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -3859,7 +3859,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>13</v>
@@ -3903,7 +3903,7 @@
         <v>18.900000000000002</v>
       </c>
       <c r="R17" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -3911,7 +3911,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>31</v>
@@ -3955,7 +3955,7 @@
         <v>18.850000000000001</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -3963,7 +3963,7 @@
         <v>46</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>99</v>
@@ -4007,7 +4007,7 @@
         <v>18.850000000000001</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -4015,7 +4015,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>26</v>
@@ -4055,7 +4055,7 @@
         <v>18.8</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -4063,7 +4063,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>67</v>
@@ -4105,7 +4105,7 @@
         <v>18.8</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4113,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>10</v>
@@ -4155,7 +4155,7 @@
         <v>18.75</v>
       </c>
       <c r="R22" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
@@ -4163,10 +4163,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D23" s="9">
         <v>1</v>
@@ -4178,7 +4178,7 @@
         <v>34</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="9"/>
@@ -4205,7 +4205,7 @@
         <v>18.75</v>
       </c>
       <c r="R23" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4213,7 +4213,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>45</v>
@@ -4255,7 +4255,7 @@
         <v>18.7</v>
       </c>
       <c r="R24" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -4263,7 +4263,7 @@
         <v>39</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>88</v>
@@ -4305,7 +4305,7 @@
         <v>18.649999999999999</v>
       </c>
       <c r="R25" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4313,7 +4313,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>36</v>
@@ -4355,7 +4355,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R26" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -4363,7 +4363,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>65</v>
@@ -4378,7 +4378,7 @@
         <v>34</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9" t="s">
@@ -4407,7 +4407,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R27" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -4415,7 +4415,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>73</v>
@@ -4457,7 +4457,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R28" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -4465,7 +4465,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>78</v>
@@ -4507,7 +4507,7 @@
         <v>18.5</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -4515,7 +4515,7 @@
         <v>21</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>57</v>
@@ -4559,7 +4559,7 @@
         <v>18.450000000000003</v>
       </c>
       <c r="R30" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4567,7 +4567,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>19</v>
@@ -4607,7 +4607,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="R31" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -4615,7 +4615,7 @@
         <v>47</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>102</v>
@@ -4659,7 +4659,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="R32" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -4667,7 +4667,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>17</v>
@@ -4711,7 +4711,7 @@
         <v>18.250000000000004</v>
       </c>
       <c r="R33" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4719,7 +4719,7 @@
         <v>13</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>39</v>
@@ -4759,7 +4759,7 @@
         <v>18.25</v>
       </c>
       <c r="R34" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="60" x14ac:dyDescent="0.2">
@@ -4767,7 +4767,7 @@
         <v>45</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>97</v>
@@ -4809,7 +4809,7 @@
         <v>18.200000000000003</v>
       </c>
       <c r="R35" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
@@ -4817,10 +4817,10 @@
         <v>49</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D36" s="4">
         <v>2</v>
@@ -4832,7 +4832,7 @@
         <v>34</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -4861,7 +4861,7 @@
         <v>15.3</v>
       </c>
       <c r="R36" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
@@ -4869,7 +4869,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>76</v>
@@ -4884,7 +4884,7 @@
         <v>77</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -4911,7 +4911,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="R37" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -4919,7 +4919,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>30</v>
@@ -4957,7 +4957,7 @@
         <v>17.8</v>
       </c>
       <c r="R38" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -4965,7 +4965,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>85</v>
@@ -4978,10 +4978,10 @@
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H39" s="28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
@@ -5007,7 +5007,7 @@
         <v>17.8</v>
       </c>
       <c r="R39" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -5015,7 +5015,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>86</v>
@@ -5057,7 +5057,7 @@
         <v>17.55</v>
       </c>
       <c r="R40" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
@@ -5065,7 +5065,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>91</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>59</v>
@@ -5107,7 +5107,7 @@
         <v>17.400000000000002</v>
       </c>
       <c r="R41" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -5115,7 +5115,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>20</v>
@@ -5130,7 +5130,7 @@
         <v>21</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>22</v>
@@ -5159,7 +5159,7 @@
         <v>17.350000000000001</v>
       </c>
       <c r="R42" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -5167,7 +5167,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>40</v>
@@ -5209,7 +5209,7 @@
         <v>17.350000000000001</v>
       </c>
       <c r="R43" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -5217,7 +5217,7 @@
         <v>24</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>63</v>
@@ -5232,7 +5232,7 @@
         <v>34</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -5259,7 +5259,7 @@
         <v>17.25</v>
       </c>
       <c r="R44" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -5267,7 +5267,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>64</v>
@@ -5311,7 +5311,7 @@
         <v>17.2</v>
       </c>
       <c r="R45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="30" x14ac:dyDescent="0.2">
@@ -5319,7 +5319,7 @@
         <v>19</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>52</v>
@@ -5363,7 +5363,7 @@
         <v>16.900000000000002</v>
       </c>
       <c r="R46" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="45" x14ac:dyDescent="0.2">
@@ -5371,7 +5371,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>23</v>
@@ -5415,7 +5415,7 @@
         <v>16.650000000000002</v>
       </c>
       <c r="R47" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -5423,7 +5423,7 @@
         <v>36</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>83</v>
@@ -5465,7 +5465,7 @@
         <v>16</v>
       </c>
       <c r="R48" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -5473,7 +5473,7 @@
         <v>33</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>38</v>
@@ -5488,7 +5488,7 @@
         <v>21</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H49" s="9" t="s">
         <v>80</v>
@@ -5517,7 +5517,7 @@
         <v>15.8</v>
       </c>
       <c r="R49" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
@@ -5525,7 +5525,7 @@
         <v>8</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C50" s="27" t="s">
         <v>28</v>
@@ -5540,7 +5540,7 @@
         <v>21</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H50" s="27" t="s">
         <v>29</v>
@@ -5569,7 +5569,7 @@
         <v>15.200000000000001</v>
       </c>
       <c r="R50" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="7" spans="1:17" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -5709,7 +5709,7 @@
     </row>
     <row r="8" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>152</v>
@@ -5732,7 +5732,7 @@
     </row>
     <row r="9" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>153</v>
@@ -5755,7 +5755,7 @@
     </row>
     <row r="10" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>140</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="11" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>141</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="12" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>142</v>
@@ -5861,7 +5861,7 @@
         <v>143</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -5884,7 +5884,7 @@
         <v>144</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -5907,7 +5907,7 @@
         <v>145</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -5930,7 +5930,7 @@
         <v>146</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -5953,7 +5953,7 @@
         <v>147</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -5999,7 +5999,7 @@
         <v>149</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -6042,10 +6042,10 @@
     </row>
     <row r="24" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="25" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -6115,21 +6115,21 @@
   <sheetData>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B5" s="34"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A7)</f>
@@ -6138,7 +6138,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A8)</f>
@@ -6147,7 +6147,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A9)</f>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B10" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A10)</f>
@@ -6165,7 +6165,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A11)</f>
@@ -6177,15 +6177,15 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B14" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A14)</f>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B15" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A15)</f>
@@ -6203,7 +6203,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B16" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A16)</f>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B17" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A17)</f>

--- a/英雄相关/角色列表.xlsx
+++ b/英雄相关/角色列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6A9321-B712-4D13-B3F8-7748A5757F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B90FD37-BAE4-49BE-B457-998DDD975E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="4800" windowWidth="28800" windowHeight="15645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9915" yWindow="4485" windowWidth="28800" windowHeight="15645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色列表" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="223">
   <si>
     <t>No.</t>
   </si>
@@ -78,9 +78,6 @@
     <t>&lt;疾行&gt;</t>
   </si>
   <si>
-    <t>己方回合开始时，在战场中的空地随机放置两个随机的增益道具。</t>
-  </si>
-  <si>
     <t>对攻击力收益大的角色，比如多倍伤害，AOE等</t>
   </si>
   <si>
@@ -334,9 +331,6 @@
   </si>
   <si>
     <t>&lt;渗透&gt;</t>
-  </si>
-  <si>
-    <t>攻击后，令敌人获得[附体]。</t>
   </si>
   <si>
     <t>共鸣者</t>
@@ -504,10 +498,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>能使敌人位移的角色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>需搭配坦克</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1135,10 +1125,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>复仇者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>白板</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2390,6 +2376,74 @@
   </si>
   <si>
     <t>我方回合开始时，随机变为己方队伍中的一名其他角色，暂时获得其所有技能和特性，直到下次变化为止。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远程
+后勤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能使敌人位移的角色，除了暗域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以移动到任意格子。攻击后，令敌人获得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>附体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>己方回合开始时，在战场中的空地随机放置两个随机的增益道具，生成增益道具只能我方拾取，对方拾取则消失</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2629,7 +2683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2695,9 +2749,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2706,9 +2757,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2733,6 +2781,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3033,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>1</v>
@@ -3063,756 +3114,740 @@
         <v>9</v>
       </c>
       <c r="L1" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="P1" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q1" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>125</v>
-      </c>
       <c r="R1" s="14" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="D2" s="9">
         <v>3</v>
       </c>
       <c r="E2" s="9">
-        <v>20</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>217</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F2" s="9"/>
       <c r="G2" s="20" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I2" s="11"/>
+        <v>12</v>
+      </c>
+      <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="10">
-        <f t="shared" ref="L2:L33" si="0">D2*2.2+E2*0.45</f>
-        <v>15.600000000000001</v>
+        <f>D2*2.2+E2*0.45</f>
+        <v>18.75</v>
       </c>
       <c r="M2" s="10">
-        <f t="shared" ref="M2:M33" si="1">SUM(IF(ISNUMBER(SEARCH("疾行",F2)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F2)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F2)),-1,0), IF(ISNUMBER(SEARCH("后勤",F2)),1,0))</f>
-        <v>3</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F2)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F2)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F2)),-1,0), IF(ISNUMBER(SEARCH("后勤",F2)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N2" s="10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O2" s="10">
         <f>N2*2.2</f>
-        <v>3.3000000000000003</v>
+        <v>0</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="10">
-        <f t="shared" ref="Q2:Q33" si="2">L2+M2+O2+P2</f>
-        <v>21.900000000000002</v>
+        <f>L2+M2+O2+P2</f>
+        <v>18.75</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="57" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="69" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D3" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="9">
+        <v>24</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>128</v>
-      </c>
+      <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
       <c r="L3" s="10">
-        <f t="shared" si="0"/>
-        <v>13.350000000000001</v>
+        <f>D3*2.2+E3*0.45</f>
+        <v>15.200000000000001</v>
       </c>
       <c r="M3" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F3)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F3)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F3)),-1,0), IF(ISNUMBER(SEARCH("后勤",F3)),1,0))</f>
         <v>1.5</v>
       </c>
       <c r="N3" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" s="10">
         <f>N3*2.2</f>
-        <v>6.6000000000000005</v>
-      </c>
-      <c r="P3" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="P3" s="10">
+        <v>1</v>
+      </c>
       <c r="Q3" s="10">
-        <f t="shared" si="2"/>
-        <v>21.450000000000003</v>
+        <f>L3+M3+O3+P3</f>
+        <v>17.700000000000003</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>166</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="D4" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" s="9">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F4" s="9"/>
-      <c r="G4" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
+      <c r="G4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>127</v>
+      </c>
       <c r="K4" s="9"/>
       <c r="L4" s="10">
-        <f t="shared" si="0"/>
-        <v>16.850000000000001</v>
+        <f>D4*2.2+E4*0.45</f>
+        <v>11.650000000000002</v>
       </c>
       <c r="M4" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F4)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F4)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F4)),-1,0), IF(ISNUMBER(SEARCH("后勤",F4)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N4" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" s="10">
         <f>N4*2.2</f>
-        <v>4.4000000000000004</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
-        <f t="shared" si="2"/>
-        <v>21.25</v>
+        <f>L4+M4+O4+P4</f>
+        <v>18.250000000000004</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D5" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>220</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="10">
-        <f t="shared" si="0"/>
-        <v>14.25</v>
+        <f>D5*2.2+E5*0.45</f>
+        <v>16.899999999999999</v>
       </c>
       <c r="M5" s="10">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F5)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F5)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F5)),-1,0), IF(ISNUMBER(SEARCH("后勤",F5)),1,0))</f>
+        <v>1.5</v>
       </c>
       <c r="N5" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" s="10">
         <f>N5*2.2</f>
-        <v>4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="P5" s="10"/>
       <c r="Q5" s="10">
-        <f t="shared" si="2"/>
-        <v>21.15</v>
+        <f>L5+M5+O5+P5</f>
+        <v>18.399999999999999</v>
       </c>
       <c r="R5" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D6" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="9">
+        <v>19</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="10">
-        <f t="shared" si="0"/>
-        <v>13.850000000000001</v>
+        <f>D6*2.2+E6*0.45</f>
+        <v>15.150000000000002</v>
       </c>
       <c r="M6" s="10">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F6)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F6)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F6)),-1,0), IF(ISNUMBER(SEARCH("后勤",F6)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N6" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O6" s="10">
-        <f>N6*0.45</f>
-        <v>1.35</v>
-      </c>
-      <c r="P6" s="10">
-        <v>4</v>
-      </c>
+        <f>N6*2.2</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P6" s="10"/>
       <c r="Q6" s="10">
-        <f t="shared" si="2"/>
-        <v>18.200000000000003</v>
+        <f>L6+M6+O6+P6</f>
+        <v>17.350000000000001</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="D7" s="9">
         <v>3</v>
       </c>
       <c r="E7" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="10">
-        <f t="shared" si="0"/>
-        <v>14.7</v>
+        <f>D7*2.2+E7*0.45</f>
+        <v>13.8</v>
       </c>
       <c r="M7" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F7)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F7)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F7)),-1,0), IF(ISNUMBER(SEARCH("后勤",F7)),1,0))</f>
         <v>1.5</v>
       </c>
       <c r="N7" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" s="10">
-        <f t="shared" ref="O7:O22" si="3">N7*2.2</f>
-        <v>4.4000000000000004</v>
+        <f>N7*0.45</f>
+        <v>1.35</v>
       </c>
       <c r="P7" s="10"/>
       <c r="Q7" s="10">
-        <f t="shared" si="2"/>
-        <v>20.6</v>
+        <f>L7+M7+O7+P7</f>
+        <v>16.650000000000002</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="D8" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" s="9">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="H8" s="9"/>
+        <v>132</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="10">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
+        <f>D8*2.2+E8*0.45</f>
+        <v>17.3</v>
       </c>
       <c r="M8" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F8)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F8)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F8)),-1,0), IF(ISNUMBER(SEARCH("后勤",F8)),1,0))</f>
         <v>1.5</v>
       </c>
-      <c r="N8" s="10">
-        <v>3</v>
-      </c>
+      <c r="N8" s="10"/>
       <c r="O8" s="10">
-        <f t="shared" si="3"/>
-        <v>6.6000000000000005</v>
+        <f>N8*2.2</f>
+        <v>0</v>
       </c>
       <c r="P8" s="10"/>
       <c r="Q8" s="10">
-        <f t="shared" si="2"/>
-        <v>20.6</v>
+        <f>L8+M8+O8+P8</f>
+        <v>18.8</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="69" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="D9" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="9">
         <v>20</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>130</v>
+      <c r="F9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
-      <c r="K9" s="12"/>
+      <c r="K9" s="9"/>
       <c r="L9" s="10">
-        <f t="shared" si="0"/>
-        <v>15.600000000000001</v>
+        <f>D9*2.2+E9*0.45</f>
+        <v>13.4</v>
       </c>
       <c r="M9" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F9)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F9)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F9)),-1,0), IF(ISNUMBER(SEARCH("后勤",F9)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N9" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" s="10">
-        <f t="shared" si="3"/>
-        <v>4.4000000000000004</v>
+        <f>N9*0.45</f>
+        <v>1.8</v>
       </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="10">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <f>L9+M9+O9+P9</f>
+        <v>15.200000000000001</v>
       </c>
       <c r="R9" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>172</v>
+        <v>162</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="D10" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="9">
         <v>20</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>131</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="10">
-        <f t="shared" si="0"/>
-        <v>15.600000000000001</v>
+        <f>D10*2.2+E10*0.45</f>
+        <v>17.8</v>
       </c>
       <c r="M10" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F10)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F10)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F10)),-1,0), IF(ISNUMBER(SEARCH("后勤",F10)),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="10">
-        <v>2</v>
-      </c>
+      <c r="N10" s="10"/>
       <c r="O10" s="10">
-        <f t="shared" si="3"/>
-        <v>4.4000000000000004</v>
+        <f>N10*2.2</f>
+        <v>0</v>
       </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="10">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <f>L10+M10+O10+P10</f>
+        <v>17.8</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="9">
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>185</v>
+        <v>132</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>31</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>56</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="10">
-        <f t="shared" si="0"/>
-        <v>15.150000000000002</v>
+        <f>D11*2.2+E11*0.45</f>
+        <v>12.950000000000001</v>
       </c>
       <c r="M11" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F11)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F11)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F11)),-1,0), IF(ISNUMBER(SEARCH("后勤",F11)),1,0))</f>
+        <v>1.5</v>
       </c>
       <c r="N11" s="10">
         <v>2</v>
       </c>
       <c r="O11" s="10">
-        <f t="shared" si="3"/>
+        <f>N11*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P11" s="10"/>
       <c r="Q11" s="10">
-        <f t="shared" si="2"/>
-        <v>19.550000000000004</v>
+        <f>L11+M11+O11+P11</f>
+        <v>18.850000000000001</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D12" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="9">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>29</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="10">
-        <f t="shared" si="0"/>
-        <v>14.7</v>
+        <f>D12*2.2+E12*0.45</f>
+        <v>20.2</v>
       </c>
       <c r="M12" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F12)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F12)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F12)),-1,0), IF(ISNUMBER(SEARCH("后勤",F12)),1,0))</f>
+        <v>-1</v>
       </c>
       <c r="N12" s="10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O12" s="10">
-        <f t="shared" si="3"/>
-        <v>3.3000000000000003</v>
+        <f>N12*2.2</f>
+        <v>0</v>
       </c>
       <c r="P12" s="10"/>
       <c r="Q12" s="10">
-        <f t="shared" si="2"/>
-        <v>19.5</v>
+        <f>L12+M12+O12+P12</f>
+        <v>19.2</v>
       </c>
       <c r="R12" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D13" s="9">
         <v>2</v>
       </c>
       <c r="E13" s="9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="10">
-        <f t="shared" si="0"/>
-        <v>16.100000000000001</v>
+        <f>D13*2.2+E13*0.45</f>
+        <v>15.200000000000001</v>
       </c>
       <c r="M13" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F13)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F13)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F13)),-1,0), IF(ISNUMBER(SEARCH("后勤",F13)),1,0))</f>
         <v>-1</v>
       </c>
       <c r="N13" s="10">
         <v>2</v>
       </c>
       <c r="O13" s="10">
-        <f t="shared" si="3"/>
+        <f>N13*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="10">
-        <f t="shared" si="2"/>
-        <v>19.5</v>
+        <f>L13+M13+O13+P13</f>
+        <v>18.600000000000001</v>
       </c>
       <c r="R13" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="D14" s="9">
         <v>2</v>
       </c>
       <c r="E14" s="9">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>95</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G14" s="20"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="9" t="s">
-        <v>96</v>
-      </c>
+      <c r="I14" s="9"/>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="10">
-        <f t="shared" si="0"/>
-        <v>16.100000000000001</v>
+        <f>D14*2.2+E14*0.45</f>
+        <v>19.25</v>
       </c>
       <c r="M14" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F14)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F14)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F14)),-1,0), IF(ISNUMBER(SEARCH("后勤",F14)),1,0))</f>
         <v>-1</v>
       </c>
       <c r="N14" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" s="10">
-        <f t="shared" si="3"/>
-        <v>4.4000000000000004</v>
+        <f>N14*2.2</f>
+        <v>0</v>
       </c>
       <c r="P14" s="10"/>
       <c r="Q14" s="10">
-        <f t="shared" si="2"/>
-        <v>19.5</v>
+        <f>L14+M14+O14+P14</f>
+        <v>18.25</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="45" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D15" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="9">
+        <v>15</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="9"/>
+      <c r="H15" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="10">
-        <f t="shared" si="0"/>
-        <v>20.2</v>
+        <f>D15*2.2+E15*0.45</f>
+        <v>15.55</v>
       </c>
       <c r="M15" s="10">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F15)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F15)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F15)),-1,0), IF(ISNUMBER(SEARCH("后勤",F15)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N15" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="10">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>N15*0.45</f>
+        <v>1.8</v>
       </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="10">
-        <f t="shared" si="2"/>
-        <v>19.2</v>
+        <f>L15+M15+O15+P15</f>
+        <v>17.350000000000001</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D16" s="9">
         <v>3</v>
@@ -3820,376 +3855,386 @@
       <c r="E16" s="9">
         <v>18</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>128</v>
+      <c r="F16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="10">
-        <f t="shared" si="0"/>
+        <f>D16*2.2+E16*0.45</f>
         <v>14.7</v>
       </c>
       <c r="M16" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F16)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F16)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F16)),-1,0), IF(ISNUMBER(SEARCH("后勤",F16)),1,0))</f>
+        <v>1.5</v>
       </c>
       <c r="N16" s="10">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O16" s="10">
-        <f t="shared" si="3"/>
-        <v>4.4000000000000004</v>
+        <f>N16*2.2</f>
+        <v>3.3000000000000003</v>
       </c>
       <c r="P16" s="10"/>
       <c r="Q16" s="10">
-        <f t="shared" si="2"/>
-        <v>19.100000000000001</v>
+        <f>L16+M16+O16+P16</f>
+        <v>19.5</v>
       </c>
       <c r="R16" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D17" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="9">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>16</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="10">
-        <f t="shared" si="0"/>
-        <v>15.200000000000001</v>
+        <f>D17*2.2+E17*0.45</f>
+        <v>16</v>
       </c>
       <c r="M17" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F17)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F17)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F17)),-1,0), IF(ISNUMBER(SEARCH("后勤",F17)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N17" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O17" s="10">
-        <f t="shared" si="3"/>
-        <v>2.2000000000000002</v>
+        <f>N17*0.45</f>
+        <v>2.7</v>
       </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10">
-        <f t="shared" si="2"/>
-        <v>18.900000000000002</v>
+        <f>L17+M17+O17+P17</f>
+        <v>18.7</v>
       </c>
       <c r="R17" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D18" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>29</v>
+        <v>48</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="10">
-        <f t="shared" si="0"/>
-        <v>12.950000000000001</v>
+        <f>D18*2.2+E18*0.45</f>
+        <v>14.25</v>
       </c>
       <c r="M18" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F18)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F18)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F18)),-1,0), IF(ISNUMBER(SEARCH("后勤",F18)),1,0))</f>
+        <v>2.5</v>
       </c>
       <c r="N18" s="10">
         <v>2</v>
       </c>
       <c r="O18" s="10">
-        <f t="shared" si="3"/>
+        <f>N18*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="10">
-        <f t="shared" si="2"/>
-        <v>18.850000000000001</v>
+        <f>L18+M18+O18+P18</f>
+        <v>21.15</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="D19" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="11" t="s">
-        <v>161</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="10">
-        <f t="shared" si="0"/>
-        <v>12.950000000000001</v>
+        <f>D19*2.2+E19*0.45</f>
+        <v>14.7</v>
       </c>
       <c r="M19" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F19)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F19)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F19)),-1,0), IF(ISNUMBER(SEARCH("后勤",F19)),1,0))</f>
         <v>1.5</v>
       </c>
       <c r="N19" s="10">
         <v>2</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" si="3"/>
+        <f>N19*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P19" s="10"/>
       <c r="Q19" s="10">
-        <f t="shared" si="2"/>
-        <v>18.850000000000001</v>
+        <f>L19+M19+O19+P19</f>
+        <v>20.6</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D20" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="20"/>
+        <v>20</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>52</v>
+      </c>
       <c r="H20" s="9" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="10">
-        <f t="shared" si="0"/>
-        <v>17.3</v>
+        <f>D20*2.2+E20*0.45</f>
+        <v>10.3</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="N20" s="10"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F20)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F20)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F20)),-1,0), IF(ISNUMBER(SEARCH("后勤",F20)),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="10">
+        <v>3</v>
+      </c>
       <c r="O20" s="10">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>N20*2.2</f>
+        <v>6.6000000000000005</v>
       </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="10">
-        <f t="shared" si="2"/>
-        <v>18.8</v>
+        <f>L20+M20+O20+P20</f>
+        <v>16.900000000000002</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D21" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="9">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+        <v>182</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>55</v>
+      </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="10">
-        <f t="shared" si="0"/>
-        <v>16.100000000000001</v>
+        <f>D21*2.2+E21*0.45</f>
+        <v>15.150000000000002</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F21)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F21)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F21)),-1,0), IF(ISNUMBER(SEARCH("后勤",F21)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N21" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" si="3"/>
-        <v>2.2000000000000002</v>
+        <f>N21*2.2</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P21" s="10"/>
       <c r="Q21" s="10">
-        <f t="shared" si="2"/>
-        <v>18.8</v>
+        <f>L21+M21+O21+P21</f>
+        <v>19.550000000000004</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D22" s="9">
         <v>3</v>
       </c>
       <c r="E22" s="9">
-        <v>27</v>
-      </c>
-      <c r="F22" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="G22" s="20" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="10">
-        <f t="shared" si="0"/>
-        <v>18.75</v>
+        <f>D22*2.2+E22*0.45</f>
+        <v>15.150000000000002</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F22)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F22)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F22)),-1,0), IF(ISNUMBER(SEARCH("后勤",F22)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N22" s="10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>N22*2.2</f>
+        <v>3.3000000000000003</v>
       </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="10">
-        <f t="shared" si="2"/>
-        <v>18.75</v>
+        <f>L22+M22+O22+P22</f>
+        <v>18.450000000000003</v>
       </c>
       <c r="R22" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>197</v>
+        <v>165</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="D23" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="9">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="H23" s="11"/>
+        <v>33</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="10">
-        <f t="shared" si="0"/>
-        <v>18.399999999999999</v>
+        <f>D23*2.2+E23*0.45</f>
+        <v>13.850000000000001</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F23)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F23)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F23)),-1,0), IF(ISNUMBER(SEARCH("后勤",F23)),1,0))</f>
         <v>-1</v>
       </c>
       <c r="N23" s="10">
@@ -4199,124 +4244,126 @@
         <f>N23*0.45</f>
         <v>1.35</v>
       </c>
-      <c r="P23" s="10"/>
+      <c r="P23" s="10">
+        <v>4</v>
+      </c>
       <c r="Q23" s="10">
-        <f t="shared" si="2"/>
-        <v>18.75</v>
+        <f>L23+M23+O23+P23</f>
+        <v>18.200000000000003</v>
       </c>
       <c r="R23" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D24" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" s="9">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="10">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>D24*2.2+E24*0.45</f>
+        <v>16.100000000000001</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F24)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F24)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F24)),-1,0), IF(ISNUMBER(SEARCH("后勤",F24)),1,0))</f>
+        <v>-1</v>
       </c>
       <c r="N24" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O24" s="10">
-        <f>N24*0.45</f>
-        <v>2.7</v>
+        <f>N24*2.2</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P24" s="10"/>
       <c r="Q24" s="10">
-        <f t="shared" si="2"/>
-        <v>18.7</v>
+        <f>L24+M24+O24+P24</f>
+        <v>19.5</v>
       </c>
       <c r="R24" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D25" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="10">
-        <f t="shared" si="0"/>
-        <v>14.25</v>
+        <f>D25*2.2+E25*0.45</f>
+        <v>13.850000000000001</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F25)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F25)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F25)),-1,0), IF(ISNUMBER(SEARCH("后勤",F25)),1,0))</f>
+        <v>-1</v>
       </c>
       <c r="N25" s="10">
         <v>2</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" ref="O25:O35" si="4">N25*2.2</f>
+        <f>N25*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P25" s="10"/>
       <c r="Q25" s="10">
-        <f t="shared" si="2"/>
-        <v>18.649999999999999</v>
+        <f>L25+M25+O25+P25</f>
+        <v>17.25</v>
       </c>
       <c r="R25" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D26" s="9">
         <v>2</v>
@@ -4325,1267 +4372,1291 @@
         <v>24</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>207</v>
       </c>
       <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
+      <c r="I26" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="10">
-        <f t="shared" si="0"/>
+        <f>D26*2.2+E26*0.45</f>
         <v>15.200000000000001</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F26)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F26)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F26)),-1,0), IF(ISNUMBER(SEARCH("后勤",F26)),1,0))</f>
         <v>-1</v>
       </c>
       <c r="N26" s="10">
         <v>2</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="4"/>
+        <f>N26*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P26" s="10"/>
       <c r="Q26" s="10">
-        <f t="shared" si="2"/>
+        <f>L26+M26+O26+P26</f>
         <v>18.600000000000001</v>
       </c>
       <c r="R26" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D27" s="9">
         <v>2</v>
       </c>
       <c r="E27" s="9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>211</v>
+        <v>131</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="H27" s="9"/>
-      <c r="I27" s="9" t="s">
-        <v>66</v>
-      </c>
+      <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="10">
-        <f t="shared" si="0"/>
-        <v>15.200000000000001</v>
+        <f>D27*2.2+E27*0.45</f>
+        <v>16.100000000000001</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F27)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F27)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F27)),-1,0), IF(ISNUMBER(SEARCH("后勤",F27)),1,0))</f>
+        <v>0.5</v>
       </c>
       <c r="N27" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" si="4"/>
-        <v>4.4000000000000004</v>
+        <f>N27*2.2</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="P27" s="10"/>
       <c r="Q27" s="10">
-        <f t="shared" si="2"/>
-        <v>18.600000000000001</v>
+        <f>L27+M27+O27+P27</f>
+        <v>18.8</v>
       </c>
       <c r="R27" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D28" s="9">
         <v>3</v>
       </c>
       <c r="E28" s="9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+        <v>69</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="11"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="10">
-        <f t="shared" si="0"/>
-        <v>13.8</v>
+        <f>D28*2.2+E28*0.45</f>
+        <v>15.600000000000001</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F28)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F28)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F28)),-1,0), IF(ISNUMBER(SEARCH("后勤",F28)),1,0))</f>
+        <v>3</v>
       </c>
       <c r="N28" s="10">
         <v>1.5</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" si="4"/>
+        <f>N28*2.2</f>
         <v>3.3000000000000003</v>
       </c>
       <c r="P28" s="10"/>
       <c r="Q28" s="10">
-        <f t="shared" si="2"/>
-        <v>18.600000000000001</v>
+        <f>L28+M28+O28+P28</f>
+        <v>21.900000000000002</v>
       </c>
       <c r="R28" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D29" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="9">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F29" s="9"/>
-      <c r="G29" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>29</v>
+      <c r="G29" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="10">
-        <f t="shared" si="0"/>
-        <v>15.200000000000001</v>
+        <f>D29*2.2+E29*0.45</f>
+        <v>14.7</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F29)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F29)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F29)),-1,0), IF(ISNUMBER(SEARCH("后勤",F29)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="4"/>
-        <v>3.3000000000000003</v>
+        <f>N29*2.2</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P29" s="10"/>
       <c r="Q29" s="10">
-        <f t="shared" si="2"/>
-        <v>18.5</v>
+        <f>L29+M29+O29+P29</f>
+        <v>19.100000000000001</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D30" s="9">
         <v>3</v>
       </c>
       <c r="E30" s="9">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>59</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H30" s="9"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="10">
-        <f t="shared" si="0"/>
-        <v>15.150000000000002</v>
+        <f>D30*2.2+E30*0.45</f>
+        <v>13.8</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F30)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F30)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F30)),-1,0), IF(ISNUMBER(SEARCH("后勤",F30)),1,0))</f>
+        <v>1.5</v>
       </c>
       <c r="N30" s="10">
         <v>1.5</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="4"/>
+        <f>N30*2.2</f>
         <v>3.3000000000000003</v>
       </c>
       <c r="P30" s="10"/>
       <c r="Q30" s="10">
-        <f t="shared" si="2"/>
-        <v>18.450000000000003</v>
+        <f>L30+M30+O30+P30</f>
+        <v>18.600000000000001</v>
       </c>
       <c r="R30" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="69" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D31" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="9">
-        <v>18</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
+      <c r="K31" s="12"/>
       <c r="L31" s="10">
-        <f t="shared" si="0"/>
-        <v>16.899999999999999</v>
+        <f>D31*2.2+E31*0.45</f>
+        <v>15.600000000000001</v>
       </c>
       <c r="M31" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F31)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F31)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F31)),-1,0), IF(ISNUMBER(SEARCH("后勤",F31)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N31" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>N31*2.2</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P31" s="10"/>
       <c r="Q31" s="10">
-        <f t="shared" si="2"/>
-        <v>18.399999999999999</v>
+        <f>L31+M31+O31+P31</f>
+        <v>20</v>
       </c>
       <c r="R31" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>31</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="9">
-        <v>47</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>169</v>
-      </c>
       <c r="C32" s="9" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="D32" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E32" s="9">
         <v>18</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>160</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="H32" s="9"/>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
       <c r="L32" s="10">
-        <f t="shared" si="0"/>
-        <v>8.1</v>
+        <f>D32*2.2+E32*0.45</f>
+        <v>14.7</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F32)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F32)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F32)),-1,0), IF(ISNUMBER(SEARCH("后勤",F32)),1,0))</f>
+        <v>1</v>
       </c>
       <c r="N32" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="4"/>
-        <v>8.8000000000000007</v>
+        <f>N32*2.2</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="P32" s="10"/>
       <c r="Q32" s="10">
-        <f t="shared" si="2"/>
-        <v>18.399999999999999</v>
+        <f>L32+M32+O32+P32</f>
+        <v>17.899999999999999</v>
       </c>
       <c r="R32" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="D33" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="J33" s="12" t="s">
-        <v>129</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="10">
-        <f t="shared" si="0"/>
-        <v>11.650000000000002</v>
+        <f>D33*2.2+E33*0.45</f>
+        <v>15.200000000000001</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="1"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F33)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F33)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F33)),-1,0), IF(ISNUMBER(SEARCH("后勤",F33)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="4"/>
-        <v>6.6000000000000005</v>
+        <f>N33*2.2</f>
+        <v>3.3000000000000003</v>
       </c>
       <c r="P33" s="10"/>
       <c r="Q33" s="10">
-        <f t="shared" si="2"/>
-        <v>18.250000000000004</v>
+        <f>L33+M33+O33+P33</f>
+        <v>18.5</v>
       </c>
       <c r="R33" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D34" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="9">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G34" s="20"/>
-      <c r="H34" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="10">
-        <f t="shared" ref="L34:L50" si="5">D34*2.2+E34*0.45</f>
-        <v>19.25</v>
+        <f>D34*2.2+E34*0.45</f>
+        <v>10.3</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" ref="M34:M50" si="6">SUM(IF(ISNUMBER(SEARCH("疾行",F34)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F34)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F34)),-1,0), IF(ISNUMBER(SEARCH("后勤",F34)),1,0))</f>
-        <v>-1</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F34)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F34)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F34)),-1,0), IF(ISNUMBER(SEARCH("后勤",F34)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N34" s="10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>N34*2.2</f>
+        <v>5.5</v>
       </c>
       <c r="P34" s="10"/>
       <c r="Q34" s="10">
-        <f t="shared" ref="Q34:Q50" si="7">L34+M34+O34+P34</f>
-        <v>18.25</v>
+        <f>L34+M34+O34+P34</f>
+        <v>15.8</v>
       </c>
       <c r="R34" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="60" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="57" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D35" s="9">
         <v>3</v>
       </c>
       <c r="E35" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
+        <v>81</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
       <c r="L35" s="10">
-        <f t="shared" si="5"/>
-        <v>13.8</v>
+        <f>D35*2.2+E35*0.45</f>
+        <v>13.350000000000001</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F35)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F35)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F35)),-1,0), IF(ISNUMBER(SEARCH("后勤",F35)),1,0))</f>
+        <v>1.5</v>
       </c>
       <c r="N35" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="4"/>
-        <v>4.4000000000000004</v>
+        <f>N35*2.2</f>
+        <v>6.6000000000000005</v>
       </c>
       <c r="P35" s="10"/>
       <c r="Q35" s="10">
-        <f t="shared" si="7"/>
-        <v>18.200000000000003</v>
+        <f>L35+M35+O35+P35</f>
+        <v>21.450000000000003</v>
       </c>
       <c r="R35" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
-        <v>49</v>
-      </c>
-      <c r="B36" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>35</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="9">
+        <v>3</v>
+      </c>
+      <c r="E36" s="9">
+        <v>20</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="10">
+        <f>D36*2.2+E36*0.45</f>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="M36" s="10">
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F36)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F36)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F36)),-1,0), IF(ISNUMBER(SEARCH("后勤",F36)),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="10">
+        <v>2</v>
+      </c>
+      <c r="O36" s="10">
+        <f>N36*2.2</f>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10">
+        <f>L36+M36+O36+P36</f>
+        <v>20</v>
+      </c>
+      <c r="R36" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D36" s="4">
+    </row>
+    <row r="37" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>36</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="9">
         <v>2</v>
       </c>
-      <c r="E36" s="4">
-        <v>22</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G36" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="10">
-        <f t="shared" si="5"/>
-        <v>14.3</v>
-      </c>
-      <c r="M36" s="10">
-        <f t="shared" si="6"/>
-        <v>-1</v>
-      </c>
-      <c r="N36" s="10">
-        <v>0</v>
-      </c>
-      <c r="O36" s="10">
-        <f>N36*0.45</f>
-        <v>0</v>
-      </c>
-      <c r="P36" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q36" s="10">
-        <f t="shared" si="7"/>
-        <v>15.3</v>
-      </c>
-      <c r="R36" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
-        <v>31</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="9">
-        <v>3</v>
-      </c>
       <c r="E37" s="9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>187</v>
+        <v>133</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>83</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="10">
-        <f t="shared" si="5"/>
-        <v>14.7</v>
+        <f>D37*2.2+E37*0.45</f>
+        <v>13.4</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F37)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F37)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F37)),-1,0), IF(ISNUMBER(SEARCH("后勤",F37)),1,0))</f>
+        <v>-1</v>
       </c>
       <c r="N37" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O37" s="10">
-        <f t="shared" ref="O37:O42" si="8">N37*2.2</f>
-        <v>2.2000000000000002</v>
+        <f>N37*0.45</f>
+        <v>3.6</v>
       </c>
       <c r="P37" s="10"/>
       <c r="Q37" s="10">
-        <f t="shared" si="7"/>
-        <v>17.899999999999999</v>
+        <f>L37+M37+O37+P37</f>
+        <v>16</v>
       </c>
       <c r="R37" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>166</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="D38" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" s="9">
         <v>20</v>
       </c>
-      <c r="F38" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="20"/>
-      <c r="H38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>215</v>
+      </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
       <c r="L38" s="10">
-        <f t="shared" si="5"/>
-        <v>17.8</v>
+        <f>D38*2.2+E38*0.45</f>
+        <v>13.4</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="6"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F38)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F38)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F38)),-1,0), IF(ISNUMBER(SEARCH("后勤",F38)),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N38" s="10"/>
+      <c r="N38" s="10">
+        <v>2</v>
+      </c>
       <c r="O38" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>N38*2.2</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P38" s="10"/>
       <c r="Q38" s="10">
-        <f t="shared" si="7"/>
+        <f>L38+M38+O38+P38</f>
         <v>17.8</v>
       </c>
       <c r="R38" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>85</v>
       </c>
       <c r="D39" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="9">
-        <v>20</v>
-      </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="H39" s="28" t="s">
-        <v>219</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39" s="9"/>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
       <c r="L39" s="10">
-        <f t="shared" si="5"/>
-        <v>13.4</v>
+        <f>D39*2.2+E39*0.45</f>
+        <v>12.15</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F39)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F39)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F39)),-1,0), IF(ISNUMBER(SEARCH("后勤",F39)),1,0))</f>
+        <v>1</v>
       </c>
       <c r="N39" s="10">
         <v>2</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" si="8"/>
+        <f>N39*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P39" s="10"/>
       <c r="Q39" s="10">
-        <f t="shared" si="7"/>
-        <v>17.8</v>
+        <f>L39+M39+O39+P39</f>
+        <v>17.55</v>
       </c>
       <c r="R39" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D40" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" s="9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
       <c r="L40" s="10">
-        <f t="shared" si="5"/>
-        <v>12.15</v>
+        <f>D40*2.2+E40*0.45</f>
+        <v>14.25</v>
       </c>
       <c r="M40" s="10">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F40)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F40)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F40)),-1,0), IF(ISNUMBER(SEARCH("后勤",F40)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N40" s="10">
         <v>2</v>
       </c>
       <c r="O40" s="10">
-        <f t="shared" si="8"/>
+        <f>N40*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P40" s="10"/>
       <c r="Q40" s="10">
-        <f t="shared" si="7"/>
-        <v>17.55</v>
+        <f>L40+M40+O40+P40</f>
+        <v>18.649999999999999</v>
       </c>
       <c r="R40" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D41" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E41" s="9">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>59</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="H41" s="11"/>
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
       <c r="L41" s="10">
-        <f t="shared" si="5"/>
-        <v>15.200000000000001</v>
+        <f>D41*2.2+E41*0.45</f>
+        <v>16.850000000000001</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="6"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F41)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F41)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F41)),-1,0), IF(ISNUMBER(SEARCH("后勤",F41)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N41" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" si="8"/>
-        <v>2.2000000000000002</v>
+        <f>N41*2.2</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P41" s="10"/>
       <c r="Q41" s="10">
-        <f t="shared" si="7"/>
-        <v>17.400000000000002</v>
+        <f>L41+M41+O41+P41</f>
+        <v>21.25</v>
       </c>
       <c r="R41" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D42" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" s="9">
-        <v>19</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42" s="22" t="s">
-        <v>189</v>
+        <v>24</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="21" t="s">
+        <v>184</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
       <c r="L42" s="10">
-        <f t="shared" si="5"/>
-        <v>15.150000000000002</v>
+        <f>D42*2.2+E42*0.45</f>
+        <v>15.200000000000001</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="6"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F42)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F42)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F42)),-1,0), IF(ISNUMBER(SEARCH("后勤",F42)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N42" s="10">
         <v>1</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" si="8"/>
+        <f>N42*2.2</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="P42" s="10"/>
       <c r="Q42" s="10">
-        <f t="shared" si="7"/>
-        <v>17.350000000000001</v>
+        <f>L42+M42+O42+P42</f>
+        <v>17.400000000000002</v>
       </c>
       <c r="R42" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
+        <v>42</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="9">
+        <v>2</v>
+      </c>
+      <c r="E43" s="9">
+        <v>18</v>
+      </c>
+      <c r="F43" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" s="9">
-        <v>4</v>
-      </c>
-      <c r="E43" s="9">
-        <v>15</v>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>42</v>
-      </c>
+      <c r="G43" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="H43" s="9"/>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
       <c r="L43" s="10">
-        <f t="shared" si="5"/>
-        <v>15.55</v>
+        <f>D43*2.2+E43*0.45</f>
+        <v>12.5</v>
       </c>
       <c r="M43" s="10">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F43)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F43)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F43)),-1,0), IF(ISNUMBER(SEARCH("后勤",F43)),1,0))</f>
+        <v>1.5</v>
       </c>
       <c r="N43" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O43" s="10">
-        <f>N43*0.45</f>
-        <v>1.8</v>
+        <f>N43*2.2</f>
+        <v>6.6000000000000005</v>
       </c>
       <c r="P43" s="10"/>
       <c r="Q43" s="10">
-        <f t="shared" si="7"/>
-        <v>17.350000000000001</v>
+        <f>L43+M43+O43+P43</f>
+        <v>20.6</v>
       </c>
       <c r="R43" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="30" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>63</v>
       </c>
       <c r="D44" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="9">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
       <c r="L44" s="10">
-        <f t="shared" si="5"/>
-        <v>13.850000000000001</v>
+        <f>D44*2.2+E44*0.45</f>
+        <v>8.5</v>
       </c>
       <c r="M44" s="10">
-        <f t="shared" si="6"/>
-        <v>-1</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F44)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F44)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F44)),-1,0), IF(ISNUMBER(SEARCH("后勤",F44)),1,0))</f>
+        <v>0</v>
       </c>
       <c r="N44" s="10">
+        <v>6</v>
+      </c>
+      <c r="O44" s="10">
+        <f>N44*0.45</f>
+        <v>2.7</v>
+      </c>
+      <c r="P44" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="10">
+        <f>L44+M44+O44+P44</f>
+        <v>15.2</v>
+      </c>
+      <c r="R44" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+      <c r="A45" s="9">
+        <v>44</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="9">
         <v>2</v>
       </c>
-      <c r="O44" s="10">
-        <f>N44*2.2</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10">
-        <f t="shared" si="7"/>
-        <v>17.25</v>
-      </c>
-      <c r="R44" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="9">
-        <v>43</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D45" s="9">
-        <v>1</v>
-      </c>
       <c r="E45" s="9">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
+      <c r="I45" s="9" t="s">
+        <v>95</v>
+      </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="10">
-        <f t="shared" si="5"/>
-        <v>8.5</v>
+        <f>D45*2.2+E45*0.45</f>
+        <v>16.100000000000001</v>
       </c>
       <c r="M45" s="10">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F45)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F45)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F45)),-1,0), IF(ISNUMBER(SEARCH("后勤",F45)),1,0))</f>
+        <v>-1</v>
       </c>
       <c r="N45" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O45" s="10">
-        <f>N45*0.45</f>
-        <v>2.7</v>
-      </c>
-      <c r="P45" s="10">
-        <v>6</v>
-      </c>
+        <f>N45*2.2</f>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P45" s="10"/>
       <c r="Q45" s="10">
-        <f t="shared" si="7"/>
-        <v>17.2</v>
+        <f>L45+M45+O45+P45</f>
+        <v>19.5</v>
       </c>
       <c r="R45" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D46" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>54</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="H46" s="9"/>
       <c r="I46" s="9"/>
       <c r="J46" s="9"/>
       <c r="K46" s="9"/>
       <c r="L46" s="10">
-        <f t="shared" si="5"/>
-        <v>10.3</v>
+        <f>D46*2.2+E46*0.45</f>
+        <v>13.8</v>
       </c>
       <c r="M46" s="10">
-        <f t="shared" si="6"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F46)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F46)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F46)),-1,0), IF(ISNUMBER(SEARCH("后勤",F46)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N46" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O46" s="10">
         <f>N46*2.2</f>
-        <v>6.6000000000000005</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P46" s="10"/>
       <c r="Q46" s="10">
-        <f t="shared" si="7"/>
-        <v>16.900000000000002</v>
+        <f>L46+M46+O46+P46</f>
+        <v>18.200000000000003</v>
       </c>
       <c r="R46" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="D47" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" s="9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I47" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H47" s="9"/>
+      <c r="I47" s="11" t="s">
+        <v>218</v>
+      </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
       <c r="L47" s="10">
-        <f t="shared" si="5"/>
-        <v>13.8</v>
+        <f>D47*2.2+E47*0.45</f>
+        <v>12.950000000000001</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" si="6"/>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F47)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F47)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F47)),-1,0), IF(ISNUMBER(SEARCH("后勤",F47)),1,0))</f>
         <v>1.5</v>
       </c>
       <c r="N47" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O47" s="10">
-        <f>N47*0.45</f>
-        <v>1.35</v>
+        <f>N47*2.2</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P47" s="10"/>
       <c r="Q47" s="10">
-        <f t="shared" si="7"/>
-        <v>16.650000000000002</v>
+        <f>L47+M47+O47+P47</f>
+        <v>18.850000000000001</v>
       </c>
       <c r="R47" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+      <c r="A48" s="9">
+        <v>47</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="9">
-        <v>36</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>171</v>
-      </c>
       <c r="C48" s="9" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D48" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>136</v>
+        <v>14</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="H48" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>157</v>
+      </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
       <c r="L48" s="10">
-        <f t="shared" si="5"/>
-        <v>13.4</v>
+        <f>D48*2.2+E48*0.45</f>
+        <v>8.1</v>
       </c>
       <c r="M48" s="10">
-        <f t="shared" si="6"/>
-        <v>-1</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F48)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F48)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F48)),-1,0), IF(ISNUMBER(SEARCH("后勤",F48)),1,0))</f>
+        <v>1.5</v>
       </c>
       <c r="N48" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O48" s="10">
-        <f>N48*0.45</f>
-        <v>3.6</v>
+        <f>N48*2.2</f>
+        <v>8.8000000000000007</v>
       </c>
       <c r="P48" s="10"/>
       <c r="Q48" s="10">
-        <f t="shared" si="7"/>
-        <v>16</v>
+        <f>L48+M48+O48+P48</f>
+        <v>18.399999999999999</v>
       </c>
       <c r="R48" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>38</v>
+        <v>167</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>193</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
       </c>
       <c r="E49" s="9">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="H49" s="11"/>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
       <c r="L49" s="10">
-        <f t="shared" si="5"/>
-        <v>10.3</v>
+        <f>D49*2.2+E49*0.45</f>
+        <v>18.399999999999999</v>
       </c>
       <c r="M49" s="10">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F49)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F49)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F49)),-1,0), IF(ISNUMBER(SEARCH("后勤",F49)),1,0))</f>
+        <v>-1</v>
       </c>
       <c r="N49" s="10">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O49" s="10">
-        <f>N49*2.2</f>
-        <v>5.5</v>
+        <f>N49*0.45</f>
+        <v>1.35</v>
       </c>
       <c r="P49" s="10"/>
       <c r="Q49" s="10">
-        <f t="shared" si="7"/>
-        <v>15.8</v>
+        <f>L49+M49+O49+P49</f>
+        <v>18.75</v>
       </c>
       <c r="R49" s="10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="27">
-        <v>8</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C50" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="27">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50" s="4">
         <v>2</v>
       </c>
-      <c r="E50" s="27">
-        <v>20</v>
+      <c r="E50" s="4">
+        <v>22</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="H50" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
-      <c r="K50" s="27"/>
+        <v>206</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
       <c r="L50" s="10">
-        <f t="shared" si="5"/>
-        <v>13.4</v>
+        <f>D50*2.2+E50*0.45</f>
+        <v>14.3</v>
       </c>
       <c r="M50" s="10">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N50" s="10">
-        <v>4</v>
-      </c>
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F50)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F50)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F50)),-1,0), IF(ISNUMBER(SEARCH("后勤",F50)),1,0))</f>
+        <v>-1</v>
+      </c>
+      <c r="N50" s="10"/>
       <c r="O50" s="10">
         <f>N50*0.45</f>
-        <v>1.8</v>
-      </c>
-      <c r="P50" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="10">
+        <v>4</v>
+      </c>
       <c r="Q50" s="10">
-        <f t="shared" si="7"/>
-        <v>15.200000000000001</v>
+        <f>L50+M50+O50+P50</f>
+        <v>17.3</v>
       </c>
       <c r="R50" s="10" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="9"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
+      <c r="A51" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="9">
+        <v>1</v>
+      </c>
+      <c r="E51" s="9">
+        <v>1</v>
+      </c>
       <c r="F51" s="9"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="11"/>
+      <c r="G51" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H51" s="9"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
+      <c r="L51" s="10">
+        <f>D51*2.2+E51*0.45</f>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="M51" s="10">
+        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F51)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F51)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F51)),-1,0), IF(ISNUMBER(SEARCH("后勤",F51)),1,0))</f>
+        <v>0</v>
+      </c>
       <c r="N51" s="10"/>
       <c r="O51" s="10"/>
       <c r="P51" s="10"/>
@@ -5593,37 +5664,19 @@
       <c r="R51" s="10"/>
     </row>
     <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A52" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="9">
-        <v>1</v>
-      </c>
-      <c r="E52" s="9">
-        <v>1</v>
-      </c>
+      <c r="A52" s="9"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
       <c r="F52" s="9"/>
-      <c r="G52" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="H52" s="9"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="11"/>
       <c r="I52" s="9"/>
       <c r="J52" s="9"/>
       <c r="K52" s="9"/>
-      <c r="L52" s="10">
-        <f>D52*2.2+E52*0.45</f>
-        <v>2.6500000000000004</v>
-      </c>
-      <c r="M52" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F52)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F52)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F52)),-1,0), IF(ISNUMBER(SEARCH("后勤",F52)),1,0))</f>
-        <v>0</v>
-      </c>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
       <c r="N52" s="10"/>
       <c r="O52" s="10"/>
       <c r="P52" s="10"/>
@@ -5633,7 +5686,7 @@
   </sheetData>
   <autoFilter ref="A1:R53" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R53">
-      <sortCondition descending="1" ref="Q1:Q53"/>
+      <sortCondition ref="A1:A53"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5647,37 +5700,37 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
+      <c r="A4" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
     </row>
     <row r="5" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="A5" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
     </row>
     <row r="6" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -5697,10 +5750,10 @@
     </row>
     <row r="7" spans="1:17" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -5709,10 +5762,10 @@
     </row>
     <row r="8" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -5732,10 +5785,10 @@
     </row>
     <row r="9" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -5755,10 +5808,10 @@
     </row>
     <row r="10" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -5778,10 +5831,10 @@
     </row>
     <row r="11" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -5801,10 +5854,10 @@
     </row>
     <row r="12" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -5824,21 +5877,21 @@
     </row>
     <row r="13" spans="1:17" s="7" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
+      <c r="A14" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -5858,10 +5911,10 @@
     </row>
     <row r="16" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -5881,10 +5934,10 @@
     </row>
     <row r="17" spans="1:17" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -5904,10 +5957,10 @@
     </row>
     <row r="18" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -5927,10 +5980,10 @@
     </row>
     <row r="19" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -5950,10 +6003,10 @@
     </row>
     <row r="20" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -5973,10 +6026,10 @@
     </row>
     <row r="21" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -5996,10 +6049,10 @@
     </row>
     <row r="22" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>207</v>
+        <v>146</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>203</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -6019,10 +6072,10 @@
     </row>
     <row r="23" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -6042,10 +6095,10 @@
     </row>
     <row r="24" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>208</v>
+        <v>195</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>204</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -6065,10 +6118,10 @@
     </row>
     <row r="25" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>209</v>
+        <v>198</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>205</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -6087,14 +6140,14 @@
       <c r="Q25" s="17"/>
     </row>
     <row r="26" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
+      <c r="A26" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6114,22 +6167,22 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="34"/>
+      <c r="A5" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="32"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A7)</f>
@@ -6138,7 +6191,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B8" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A8)</f>
@@ -6147,7 +6200,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B9" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A9)</f>
@@ -6156,7 +6209,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B10" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A10)</f>
@@ -6165,7 +6218,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B11" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A11)</f>
@@ -6177,15 +6230,15 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B14" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A14)</f>
@@ -6194,7 +6247,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B15" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A15)</f>
@@ -6203,7 +6256,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B16" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A16)</f>
@@ -6212,7 +6265,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B17" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A17)</f>
@@ -6238,47 +6291,47 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
+        <v>107</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E12">
         <v>18.75</v>
       </c>
-      <c r="G12" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="H12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
+      <c r="G12" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -6294,7 +6347,7 @@
         <v>18.75</v>
       </c>
       <c r="G14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -6313,7 +6366,7 @@
         <v>18.75</v>
       </c>
       <c r="G15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -6332,7 +6385,7 @@
         <v>18.75</v>
       </c>
       <c r="G16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -6351,7 +6404,7 @@
         <v>18.75</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -6370,7 +6423,7 @@
         <v>18.75</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H18">
         <v>1</v>
